--- a/day6.xlsx
+++ b/day6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FF6A10-6722-7047-B798-0E5F83FCC4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA48CDE-2742-8B47-9707-186C57ECCA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="2" xr2:uid="{CCC94A23-119C-9F45-9D42-5CBBD8A7CC54}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{CCC94A23-119C-9F45-9D42-5CBBD8A7CC54}"/>
   </bookViews>
   <sheets>
     <sheet name="AGENDA" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -247,7 +247,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -470,14 +470,8 @@
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -501,16 +495,29 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -525,16 +532,16 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -543,13 +550,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="2" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4066,8 +4066,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>41080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="40" name="Ink 39">
@@ -4086,7 +4086,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="40" name="Ink 39">
@@ -4131,8 +4131,8 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>19360</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="41" name="Ink 40">
@@ -4151,7 +4151,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="41" name="Ink 40">
@@ -4257,8 +4257,8 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>149547</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="43" name="Ink 42">
@@ -4277,7 +4277,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="43" name="Ink 42">
@@ -4322,8 +4322,8 @@
       <xdr:row>62</xdr:row>
       <xdr:rowOff>84097</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="51" name="Ink 50">
@@ -4342,7 +4342,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="51" name="Ink 50">
@@ -4387,8 +4387,8 @@
       <xdr:row>69</xdr:row>
       <xdr:rowOff>139921</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="58" name="Ink 57">
@@ -4407,7 +4407,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="58" name="Ink 57">
@@ -4457,8 +4457,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>58424</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -4477,7 +4477,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -4522,8 +4522,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>116744</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -4542,7 +4542,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -4587,8 +4587,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>28596</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -4607,7 +4607,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -4652,8 +4652,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>174396</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -4672,7 +4672,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -4717,8 +4717,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>36516</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -4737,7 +4737,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -4782,8 +4782,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>38212</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Ink 6">
@@ -4802,7 +4802,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Ink 6">
@@ -4847,8 +4847,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>43972</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Ink 7">
@@ -4867,7 +4867,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Ink 7">
@@ -4912,8 +4912,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>40012</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Ink 8">
@@ -4932,7 +4932,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Ink 8">
@@ -4977,8 +4977,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>40243</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="10" name="Ink 9">
@@ -4997,7 +4997,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="10" name="Ink 9">
@@ -5042,8 +5042,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>99480</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="Ink 13">
@@ -5062,7 +5062,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="Ink 13">
@@ -5107,8 +5107,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>40080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="22" name="Ink 21">
@@ -5127,7 +5127,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="22" name="Ink 21">
@@ -5172,8 +5172,8 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>85540</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Ink 25">
@@ -5192,7 +5192,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Ink 25">
@@ -5237,8 +5237,8 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>79579</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="30" name="Ink 29">
@@ -5257,7 +5257,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="30" name="Ink 29">
@@ -5346,8 +5346,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>13821</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="46" name="Ink 45">
@@ -5366,7 +5366,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="46" name="Ink 45">
@@ -6381,24 +6381,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
@@ -6422,16 +6422,16 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
@@ -6442,26 +6442,26 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="9" t="str">
+      <c r="C21" s="7" t="str">
         <f>"1/4"</f>
         <v>1/4</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
@@ -6469,15 +6469,15 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
@@ -6496,15 +6496,15 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
@@ -6526,15 +6526,15 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
@@ -6586,18 +6586,18 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C102" t="s">
@@ -6605,15 +6605,15 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6641,7 +6641,7 @@
       <c r="B3">
         <v>16</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>-6</v>
       </c>
       <c r="D3">
@@ -6657,7 +6657,7 @@
       <c r="B4">
         <v>14</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>-6</v>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       <c r="B5">
         <v>27</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>-5</v>
       </c>
       <c r="D5">
@@ -6673,7 +6673,7 @@
         <v>15.5</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" ref="F4:F7" ca="1" si="0">_xlfn.FORMULATEXT(D5)</f>
+        <f t="shared" ref="F5:F7" ca="1" si="0">_xlfn.FORMULATEXT(D5)</f>
         <v>=MEDIAN(B3:B22)</v>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       <c r="B6">
         <v>22</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       <c r="B7">
         <v>30</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7">
@@ -6705,19 +6705,19 @@
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>23</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>6</v>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       <c r="B10">
         <v>-5</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>9</v>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       <c r="B11">
         <v>-6</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>14</v>
       </c>
       <c r="D11">
@@ -6749,7 +6749,7 @@
       <c r="B12">
         <v>-6</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>15</v>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       <c r="B13">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>16</v>
       </c>
       <c r="D13">
@@ -6773,7 +6773,7 @@
       <c r="B14">
         <v>6</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>18</v>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       <c r="B15">
         <v>15</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>21</v>
       </c>
       <c r="D15">
@@ -6797,7 +6797,7 @@
       <c r="B16">
         <v>30</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
         <v>22</v>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
       <c r="B17">
         <v>25</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="4">
         <v>23</v>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       <c r="B18">
         <v>18</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>25</v>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       <c r="B19">
         <v>21</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>27</v>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       <c r="B20">
         <v>3</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>29</v>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       <c r="B21">
         <v>29</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>30</v>
       </c>
     </row>
@@ -6845,21 +6845,21 @@
       <c r="B22">
         <v>0</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F25" t="s">
@@ -6867,7 +6867,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E26" s="8">
+      <c r="E26" s="6">
         <v>0.3</v>
       </c>
       <c r="F26">
@@ -6887,7 +6887,7 @@
       <c r="B28">
         <v>16</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>-6</v>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       <c r="B29">
         <v>14</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>-6</v>
       </c>
       <c r="E29">
@@ -6907,7 +6907,7 @@
       <c r="B30">
         <v>27</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>-5</v>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       <c r="B31">
         <v>22</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>0</v>
       </c>
       <c r="E31">
@@ -6927,7 +6927,7 @@
       <c r="B32">
         <v>30</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       <c r="B33">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="3">
         <v>3</v>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       <c r="B34">
         <v>23</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="3">
         <v>6</v>
       </c>
       <c r="E34" t="s">
@@ -6958,7 +6958,7 @@
       <c r="B35">
         <v>-5</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="3">
         <v>9</v>
       </c>
       <c r="E35" t="s">
@@ -6973,7 +6973,7 @@
       <c r="B36">
         <v>-6</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="3">
         <v>14</v>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       <c r="B37">
         <v>-6</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="3">
         <v>15</v>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       <c r="B38">
         <v>9</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="4">
         <v>16</v>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       <c r="B39">
         <v>6</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="4">
         <v>18</v>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       <c r="B40">
         <v>15</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="4">
         <v>21</v>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       <c r="B41">
         <v>30</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="4">
         <v>22</v>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       <c r="B42">
         <v>25</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="4">
         <v>23</v>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       <c r="B43">
         <v>18</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="5">
         <v>25</v>
       </c>
     </row>
@@ -7037,7 +7037,7 @@
       <c r="B44">
         <v>21</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="5">
         <v>27</v>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       <c r="B45">
         <v>3</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="5">
         <v>29</v>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       <c r="B46">
         <v>29</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="5">
         <v>30</v>
       </c>
       <c r="D46" t="s">
@@ -7064,7 +7064,7 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="5">
         <v>30</v>
       </c>
       <c r="D47" t="s">
@@ -7072,16 +7072,16 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
@@ -7126,7 +7126,7 @@
         <f t="shared" ref="D55:D73" si="3">C55^2</f>
         <v>0.12249999999999975</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
         <f>C56^2</f>
         <v>178.2225</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F56">
@@ -7404,16 +7404,16 @@
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
@@ -7451,10 +7451,10 @@
       <c r="D87">
         <v>76</v>
       </c>
-      <c r="J87" s="39" t="s">
+      <c r="J87" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="K87" s="39" t="s">
+      <c r="K87" s="27" t="s">
         <v>40</v>
       </c>
     </row>
@@ -7468,11 +7468,11 @@
       <c r="I88" t="s">
         <v>1</v>
       </c>
-      <c r="J88" s="3">
+      <c r="J88" s="1">
         <f>AVERAGE(B84:B183)</f>
         <v>46.97</v>
       </c>
-      <c r="K88" s="3">
+      <c r="K88" s="1">
         <f>AVERAGE(D84:D106)</f>
         <v>48.869565217391305</v>
       </c>
@@ -7506,11 +7506,11 @@
       <c r="I90" t="s">
         <v>45</v>
       </c>
-      <c r="J90" s="3">
+      <c r="J90" s="1">
         <f>_xlfn.STDEV.P(B84:B183)</f>
         <v>22.000661353695712</v>
       </c>
-      <c r="K90" s="3">
+      <c r="K90" s="1">
         <f>_xlfn.STDEV.S(D84:D106)</f>
         <v>21.772176464106426</v>
       </c>
@@ -8122,13 +8122,13 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
@@ -8245,11 +8245,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40">
+      <c r="F37" s="28"/>
+      <c r="G37" s="28">
         <f>G30-1.5*G34</f>
         <v>-2.75</v>
       </c>
@@ -8271,11 +8271,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E39" s="40" t="s">
+      <c r="E39" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40">
+      <c r="F39" s="28"/>
+      <c r="G39" s="28">
         <f>G32+1.5*G34</f>
         <v>71.25</v>
       </c>
@@ -8308,19 +8308,22 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C28:C42">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -8330,9 +8333,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8349,4435 +8349,4435 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A1" s="11"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="22" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="23"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="24" t="s">
+      <c r="F1" s="38"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="26" t="s">
+      <c r="I1" s="32"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="27"/>
+      <c r="L1" s="34"/>
     </row>
     <row r="2" spans="1:26" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="15" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="32" t="s">
+      <c r="O2" s="9"/>
+      <c r="P2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="22" t="s">
+      <c r="Q2" s="40"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="23"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="24" t="s">
+      <c r="T2" s="38"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="25"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="26" t="s">
+      <c r="W2" s="32"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="27"/>
+      <c r="Z2" s="34"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="16">
+      <c r="A3" s="9"/>
+      <c r="B3" s="14">
         <v>55.993030150000003</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <v>79.277263700000006</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="17">
+      <c r="D3" s="9"/>
+      <c r="E3" s="15">
         <v>55.384599999999999</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="15">
         <v>97.179500000000004</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="18">
+      <c r="G3" s="9"/>
+      <c r="H3" s="16">
         <v>58.213608260000001</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>91.881891510000003</v>
       </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="19">
+      <c r="J3" s="9"/>
+      <c r="K3" s="17">
         <v>38.337757179999997</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="17">
         <v>92.472719049999995</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="28" t="s">
+      <c r="O3" s="9"/>
+      <c r="P3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="28" t="s">
+      <c r="Q3" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="11"/>
-      <c r="S3" s="29" t="s">
+      <c r="R3" s="9"/>
+      <c r="S3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="T3" s="29" t="s">
+      <c r="T3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="U3" s="11"/>
-      <c r="V3" s="30" t="s">
+      <c r="U3" s="9"/>
+      <c r="V3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="30" t="s">
+      <c r="W3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="31" t="s">
+      <c r="X3" s="9"/>
+      <c r="Y3" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="31" t="s">
+      <c r="Z3" s="21" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="16">
+      <c r="A4" s="9"/>
+      <c r="B4" s="14">
         <v>50.032253789999999</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="14">
         <v>79.013071199999999</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="17">
+      <c r="D4" s="9"/>
+      <c r="E4" s="15">
         <v>51.538499999999999</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="15">
         <v>96.025599999999997</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="18">
+      <c r="G4" s="9"/>
+      <c r="H4" s="16">
         <v>58.196053689999999</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="16">
         <v>92.214988649999995</v>
       </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="19">
+      <c r="J4" s="9"/>
+      <c r="K4" s="17">
         <v>35.751870789999998</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="17">
         <v>94.116768030000003</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="22">
         <f>AVERAGE($B$3:$B$144)</f>
         <v>54.26731970598594</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="22">
         <f>AVERAGE($B$3:$B$144)</f>
         <v>54.26731970598594</v>
       </c>
-      <c r="R4" s="35"/>
-      <c r="S4" s="36">
+      <c r="R4" s="23"/>
+      <c r="S4" s="24">
         <f>AVERAGE($E$3:$E$144)</f>
         <v>54.263273239436643</v>
       </c>
-      <c r="T4" s="36">
+      <c r="T4" s="24">
         <f>AVERAGE(F3:F144)</f>
         <v>47.832252816901374</v>
       </c>
-      <c r="U4" s="35"/>
-      <c r="V4" s="37">
+      <c r="U4" s="23"/>
+      <c r="V4" s="25">
         <f>AVERAGE(H3:H144)</f>
         <v>54.26734110478872</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="25">
         <f>AVERAGE(I3:I144)</f>
         <v>47.83954522535209</v>
       </c>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="38">
+      <c r="X4" s="23"/>
+      <c r="Y4" s="26">
         <f>AVERAGE(K3:K144)</f>
         <v>54.260150334154929</v>
       </c>
-      <c r="Z4" s="38">
+      <c r="Z4" s="26">
         <f>AVERAGE(L3:L144)</f>
         <v>47.839717279450717</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="16">
+      <c r="A5" s="9"/>
+      <c r="B5" s="14">
         <v>51.288458660000003</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="14">
         <v>82.435939840000003</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="17">
+      <c r="D5" s="9"/>
+      <c r="E5" s="15">
         <v>46.153799999999997</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="15">
         <v>94.487200000000001</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="18">
+      <c r="G5" s="9"/>
+      <c r="H5" s="16">
         <v>58.718230720000001</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="16">
         <v>90.310532089999995</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="19">
+      <c r="J5" s="9"/>
+      <c r="K5" s="17">
         <v>32.767217960000004</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="17">
         <v>88.518294580000003</v>
       </c>
-      <c r="O5" s="28" t="s">
+      <c r="O5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="22">
         <f>_xlfn.STDEV.P($B$3:$B$144)</f>
         <v>16.700894265150971</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="22">
         <f>_xlfn.STDEV.P($C$3:$C$144)</f>
         <v>26.835044482889582</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="22">
         <f>_xlfn.STDEV.P($E$3:$E$144)</f>
         <v>16.706005551356565</v>
       </c>
-      <c r="T5" s="34">
+      <c r="T5" s="22">
         <f>_xlfn.STDEV.P($F$3:$F$144)</f>
         <v>26.840392949306839</v>
       </c>
-      <c r="V5" s="34">
+      <c r="V5" s="22">
         <f>_xlfn.STDEV.P($H$3:$H$144)</f>
         <v>16.709809263923034</v>
       </c>
-      <c r="W5" s="34">
+      <c r="W5" s="22">
         <f>_xlfn.STDEV.P($I$3:$I$144)</f>
         <v>26.83528224151376</v>
       </c>
-      <c r="Y5" s="34">
+      <c r="Y5" s="22">
         <f>_xlfn.STDEV.P($H$3:$H$144)</f>
         <v>16.709809263923034</v>
       </c>
-      <c r="Z5" s="34">
+      <c r="Z5" s="22">
         <f>_xlfn.STDEV.P($I$3:$I$144)</f>
         <v>26.83528224151376</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="16">
+      <c r="A6" s="9"/>
+      <c r="B6" s="14">
         <v>51.170536890000001</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="14">
         <v>79.165294110000005</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="17">
+      <c r="D6" s="9"/>
+      <c r="E6" s="15">
         <v>42.820500000000003</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="15">
         <v>91.410300000000007</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="18">
+      <c r="G6" s="9"/>
+      <c r="H6" s="16">
         <v>57.278372869999998</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="16">
         <v>89.907606720000004</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="19">
+      <c r="J6" s="9"/>
+      <c r="K6" s="17">
         <v>33.729606779999997</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="17">
         <v>88.62226579</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="16">
+      <c r="A7" s="9"/>
+      <c r="B7" s="14">
         <v>44.377914529999998</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="14">
         <v>78.164627999999993</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="17">
+      <c r="D7" s="9"/>
+      <c r="E7" s="15">
         <v>40.769199999999998</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="15">
         <v>88.333299999999994</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="18">
+      <c r="G7" s="9"/>
+      <c r="H7" s="16">
         <v>58.082020489999998</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="16">
         <v>92.008145010000007</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="19">
+      <c r="J7" s="9"/>
+      <c r="K7" s="17">
         <v>37.238249330000002</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="17">
         <v>83.724928410000004</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="16">
+      <c r="A8" s="9"/>
+      <c r="B8" s="14">
         <v>45.010270069999997</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="14">
         <v>77.880863120000001</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="17">
+      <c r="D8" s="9"/>
+      <c r="E8" s="15">
         <v>38.7179</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <v>84.871799999999993</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="18">
+      <c r="G8" s="9"/>
+      <c r="H8" s="16">
         <v>57.489447769999998</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="16">
         <v>88.085285560000003</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="19">
+      <c r="J8" s="9"/>
+      <c r="K8" s="17">
         <v>36.027198220000002</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="17">
         <v>82.040780650000002</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="16">
+      <c r="A9" s="9"/>
+      <c r="B9" s="14">
         <v>48.559816720000001</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="14">
         <v>78.788370599999993</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="17">
+      <c r="D9" s="9"/>
+      <c r="E9" s="15">
         <v>35.640999999999998</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <v>79.871799999999993</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="18">
+      <c r="G9" s="9"/>
+      <c r="H9" s="16">
         <v>28.08874132</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="16">
         <v>63.510794429999997</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="19">
+      <c r="J9" s="9"/>
+      <c r="K9" s="17">
         <v>39.239280780000001</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="17">
         <v>79.263723839999997</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="16">
+      <c r="A10" s="9"/>
+      <c r="B10" s="14">
         <v>42.142268289999997</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="14">
         <v>76.880634549999996</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="17">
+      <c r="D10" s="9"/>
+      <c r="E10" s="15">
         <v>33.076900000000002</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>77.564099999999996</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="18">
+      <c r="G10" s="9"/>
+      <c r="H10" s="16">
         <v>28.085468209999998</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="16">
         <v>63.590196949999999</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="19">
+      <c r="J10" s="9"/>
+      <c r="K10" s="17">
         <v>39.784524939999997</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="17">
         <v>82.260565900000003</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="16">
+      <c r="A11" s="9"/>
+      <c r="B11" s="14">
         <v>41.026971570000001</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="14">
         <v>76.409588459999995</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="17">
+      <c r="D11" s="9"/>
+      <c r="E11" s="15">
         <v>28.974399999999999</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>74.487200000000001</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="18">
+      <c r="G11" s="9"/>
+      <c r="H11" s="16">
         <v>28.08727305</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="16">
         <v>63.123282809999999</v>
       </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="19">
+      <c r="J11" s="9"/>
+      <c r="K11" s="17">
         <v>35.166029389999999</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="17">
         <v>84.156491979999998</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
-      <c r="B12" s="16">
+      <c r="A12" s="9"/>
+      <c r="B12" s="14">
         <v>34.575309009999998</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <v>72.724841179999999</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="17">
+      <c r="D12" s="9"/>
+      <c r="E12" s="15">
         <v>26.1538</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <v>71.410300000000007</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="18">
+      <c r="G12" s="9"/>
+      <c r="H12" s="16">
         <v>27.578025220000001</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="16">
         <v>62.821038659999999</v>
       </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="19">
+      <c r="J12" s="9"/>
+      <c r="K12" s="17">
         <v>40.622115919999999</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="17">
         <v>78.542104210000005</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="16">
+      <c r="A13" s="9"/>
+      <c r="B13" s="14">
         <v>31.168600720000001</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <v>69.245421320000005</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="17">
+      <c r="D13" s="9"/>
+      <c r="E13" s="15">
         <v>23.076899999999998</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>66.410300000000007</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="18">
+      <c r="G13" s="9"/>
+      <c r="H13" s="16">
         <v>27.779919110000002</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="16">
         <v>63.518147519999999</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="19">
+      <c r="J13" s="9"/>
+      <c r="K13" s="17">
         <v>39.181907090000003</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="17">
         <v>79.819037199999997</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="16">
+      <c r="A14" s="9"/>
+      <c r="B14" s="14">
         <v>32.644254070000002</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <v>70.73255503</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="17">
+      <c r="D14" s="9"/>
+      <c r="E14" s="15">
         <v>22.307700000000001</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>61.794899999999998</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="18">
+      <c r="G14" s="9"/>
+      <c r="H14" s="16">
         <v>28.588999810000001</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="16">
         <v>63.024080570000002</v>
       </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="19">
+      <c r="J14" s="9"/>
+      <c r="K14" s="17">
         <v>42.43088899</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="17">
         <v>75.133634639999997</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="16">
+      <c r="A15" s="9"/>
+      <c r="B15" s="14">
         <v>26.66664565</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <v>62.98097121</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="17">
+      <c r="D15" s="9"/>
+      <c r="E15" s="15">
         <v>22.307700000000001</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <v>57.179499999999997</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="18">
+      <c r="G15" s="9"/>
+      <c r="H15" s="16">
         <v>28.739141499999999</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="16">
         <v>62.720863889999997</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="19">
+      <c r="J15" s="9"/>
+      <c r="K15" s="17">
         <v>43.081255859999999</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="17">
         <v>75.346701640000006</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="16">
+      <c r="A16" s="9"/>
+      <c r="B16" s="14">
         <v>26.459262330000001</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="14">
         <v>62.634673370000002</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="17">
+      <c r="D16" s="9"/>
+      <c r="E16" s="15">
         <v>23.333300000000001</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="15">
         <v>52.948700000000002</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="18">
+      <c r="G16" s="9"/>
+      <c r="H16" s="16">
         <v>27.024603240000001</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="16">
         <v>62.901858859999997</v>
       </c>
-      <c r="J16" s="11"/>
-      <c r="K16" s="19">
+      <c r="J16" s="9"/>
+      <c r="K16" s="17">
         <v>44.360719430000003</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="17">
         <v>70.474207050000004</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="16">
+      <c r="A17" s="9"/>
+      <c r="B17" s="14">
         <v>25.538007650000001</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="14">
         <v>60.630236109999998</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="17">
+      <c r="D17" s="9"/>
+      <c r="E17" s="15">
         <v>25.897400000000001</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <v>51.025599999999997</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="18">
+      <c r="G17" s="9"/>
+      <c r="H17" s="16">
         <v>28.8013367</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="16">
         <v>63.389040389999998</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="19">
+      <c r="J17" s="9"/>
+      <c r="K17" s="17">
         <v>44.32477884</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="17">
         <v>71.045904399999998</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
-      <c r="B18" s="16">
+      <c r="A18" s="9"/>
+      <c r="B18" s="14">
         <v>26.320711190000001</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="14">
         <v>62.396281119999998</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="17">
+      <c r="D18" s="9"/>
+      <c r="E18" s="15">
         <v>29.487200000000001</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="15">
         <v>51.025599999999997</v>
       </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="18">
+      <c r="G18" s="9"/>
+      <c r="H18" s="16">
         <v>27.186463839999998</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="16">
         <v>63.558729649999997</v>
       </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="19">
+      <c r="J18" s="9"/>
+      <c r="K18" s="17">
         <v>47.552160200000003</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="17">
         <v>66.460403720000002</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="16">
+      <c r="A19" s="9"/>
+      <c r="B19" s="14">
         <v>26.163387459999999</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="14">
         <v>62.026814899999998</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="17">
+      <c r="D19" s="9"/>
+      <c r="E19" s="15">
         <v>32.820500000000003</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="15">
         <v>51.025599999999997</v>
       </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="18">
+      <c r="G19" s="9"/>
+      <c r="H19" s="16">
         <v>29.285146600000001</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="16">
         <v>63.38360583</v>
       </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="19">
+      <c r="J19" s="9"/>
+      <c r="K19" s="17">
         <v>48.664924620000001</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="17">
         <v>64.961004939999995</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="B20" s="16">
+      <c r="A20" s="9"/>
+      <c r="B20" s="14">
         <v>25.213790459999998</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="14">
         <v>60.2733986</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="17">
+      <c r="D20" s="9"/>
+      <c r="E20" s="15">
         <v>35.384599999999999</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="15">
         <v>51.410299999999999</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="18">
+      <c r="G20" s="9"/>
+      <c r="H20" s="16">
         <v>39.402945299999999</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="16">
         <v>51.150857199999997</v>
       </c>
-      <c r="J20" s="11"/>
-      <c r="K20" s="19">
+      <c r="J20" s="9"/>
+      <c r="K20" s="17">
         <v>46.280631960000001</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="17">
         <v>68.028423149999995</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="16">
+      <c r="A21" s="9"/>
+      <c r="B21" s="14">
         <v>26.859529559999999</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="14">
         <v>63.141834670000001</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="17">
+      <c r="D21" s="9"/>
+      <c r="E21" s="15">
         <v>40.256399999999999</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="15">
         <v>51.410299999999999</v>
       </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="18">
+      <c r="G21" s="9"/>
+      <c r="H21" s="16">
         <v>28.81132844</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="16">
         <v>61.357854060000001</v>
       </c>
-      <c r="J21" s="11"/>
-      <c r="K21" s="19">
+      <c r="J21" s="9"/>
+      <c r="K21" s="17">
         <v>50.563244480000002</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="17">
         <v>62.623827970000001</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
-      <c r="B22" s="16">
+      <c r="A22" s="9"/>
+      <c r="B22" s="14">
         <v>31.76066917</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="14">
         <v>69.797655390000003</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="17">
+      <c r="D22" s="9"/>
+      <c r="E22" s="15">
         <v>44.102600000000002</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="15">
         <v>52.948700000000002</v>
       </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="18">
+      <c r="G22" s="9"/>
+      <c r="H22" s="16">
         <v>34.303957910000001</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="16">
         <v>56.542125910000003</v>
       </c>
-      <c r="J22" s="11"/>
-      <c r="K22" s="19">
+      <c r="J22" s="9"/>
+      <c r="K22" s="17">
         <v>52.630964229999996</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="17">
         <v>59.963935790000001</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="16">
+      <c r="A23" s="9"/>
+      <c r="B23" s="14">
         <v>39.793290570000003</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="14">
         <v>75.807964220000002</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="17">
+      <c r="D23" s="9"/>
+      <c r="E23" s="15">
         <v>46.666699999999999</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="15">
         <v>54.102600000000002</v>
       </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="18">
+      <c r="G23" s="9"/>
+      <c r="H23" s="16">
         <v>29.602760979999999</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="16">
         <v>60.15734672</v>
       </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="19">
+      <c r="J23" s="9"/>
+      <c r="K23" s="17">
         <v>54.636206440000002</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="17">
         <v>57.493842440000002</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
-      <c r="B24" s="16">
+      <c r="A24" s="9"/>
+      <c r="B24" s="14">
         <v>45.617439189999999</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>78.119970230000007</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="17">
+      <c r="D24" s="9"/>
+      <c r="E24" s="15">
         <v>50</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="15">
         <v>55.256399999999999</v>
       </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="18">
+      <c r="G24" s="9"/>
+      <c r="H24" s="16">
         <v>49.116156859999997</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="16">
         <v>63.660000619999998</v>
       </c>
-      <c r="J24" s="11"/>
-      <c r="K24" s="19">
+      <c r="J24" s="9"/>
+      <c r="K24" s="17">
         <v>51.346027139999997</v>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="17">
         <v>61.600553040000001</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="16">
+      <c r="A25" s="9"/>
+      <c r="B25" s="14">
         <v>53.771460679999997</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="14">
         <v>79.302931639999997</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="17">
+      <c r="D25" s="9"/>
+      <c r="E25" s="15">
         <v>53.076900000000002</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="15">
         <v>55.640999999999998</v>
       </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="18">
+      <c r="G25" s="9"/>
+      <c r="H25" s="16">
         <v>39.617545829999997</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="16">
         <v>62.925187960000002</v>
       </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="19">
+      <c r="J25" s="9"/>
+      <c r="K25" s="17">
         <v>57.134855350000002</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="17">
         <v>53.877965799999998</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
-      <c r="B26" s="16">
+      <c r="A26" s="9"/>
+      <c r="B26" s="14">
         <v>56.45143367</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="14">
         <v>79.247107020000001</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="17">
+      <c r="D26" s="9"/>
+      <c r="E26" s="15">
         <v>56.666699999999999</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="15">
         <v>56.025599999999997</v>
       </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="18">
+      <c r="G26" s="9"/>
+      <c r="H26" s="16">
         <v>43.233084660000003</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="16">
         <v>63.165218719999999</v>
       </c>
-      <c r="J26" s="11"/>
-      <c r="K26" s="19">
+      <c r="J26" s="9"/>
+      <c r="K26" s="17">
         <v>54.171241569999999</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="17">
         <v>58.059807900000003</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="16">
+      <c r="A27" s="9"/>
+      <c r="B27" s="14">
         <v>66.093720200000007</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="14">
         <v>77.017818259999999</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="17">
+      <c r="D27" s="9"/>
+      <c r="E27" s="15">
         <v>59.230800000000002</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="15">
         <v>57.948700000000002</v>
       </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="18">
+      <c r="G27" s="9"/>
+      <c r="H27" s="16">
         <v>64.892787940000005</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="16">
         <v>65.814176759999995</v>
       </c>
-      <c r="J27" s="11"/>
-      <c r="K27" s="19">
+      <c r="J27" s="9"/>
+      <c r="K27" s="17">
         <v>50.942382309999999</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="17">
         <v>62.097393940000003</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
-      <c r="B28" s="16">
+      <c r="A28" s="9"/>
+      <c r="B28" s="14">
         <v>56.925839420000003</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="14">
         <v>79.206318620000005</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="17">
+      <c r="D28" s="9"/>
+      <c r="E28" s="15">
         <v>61.2821</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="15">
         <v>62.179499999999997</v>
       </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="18">
+      <c r="G28" s="9"/>
+      <c r="H28" s="16">
         <v>62.49014932</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="16">
         <v>74.584289609999999</v>
       </c>
-      <c r="J28" s="11"/>
-      <c r="K28" s="19">
+      <c r="J28" s="9"/>
+      <c r="K28" s="17">
         <v>66.512924459999994</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="17">
         <v>59.071281849999998</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="16">
+      <c r="A29" s="9"/>
+      <c r="B29" s="14">
         <v>58.98825385</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="14">
         <v>78.917258959999998</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="17">
+      <c r="D29" s="9"/>
+      <c r="E29" s="15">
         <v>61.538499999999999</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="15">
         <v>66.410300000000007</v>
       </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="18">
+      <c r="G29" s="9"/>
+      <c r="H29" s="16">
         <v>68.988084430000001</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="16">
         <v>63.232147310000002</v>
       </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="19">
+      <c r="J29" s="9"/>
+      <c r="K29" s="17">
         <v>64.397909499999997</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="17">
         <v>56.174875399999998</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
-      <c r="B30" s="16">
+      <c r="A30" s="9"/>
+      <c r="B30" s="14">
         <v>57.902266050000001</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="14">
         <v>79.080867819999995</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="17">
+      <c r="D30" s="9"/>
+      <c r="E30" s="15">
         <v>61.794899999999998</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="15">
         <v>69.102599999999995</v>
       </c>
-      <c r="G30" s="11"/>
-      <c r="H30" s="18">
+      <c r="G30" s="9"/>
+      <c r="H30" s="16">
         <v>62.105618630000002</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="16">
         <v>75.990870760000007</v>
       </c>
-      <c r="J30" s="11"/>
-      <c r="K30" s="19">
+      <c r="J30" s="9"/>
+      <c r="K30" s="17">
         <v>68.686593290000005</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="17">
         <v>62.237343989999999</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="B31" s="16">
+      <c r="A31" s="9"/>
+      <c r="B31" s="14">
         <v>64.812866959999994</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="14">
         <v>77.48693892</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="17">
+      <c r="D31" s="9"/>
+      <c r="E31" s="15">
         <v>57.435899999999997</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="15">
         <v>55.256399999999999</v>
       </c>
-      <c r="G31" s="11"/>
-      <c r="H31" s="18">
+      <c r="G31" s="9"/>
+      <c r="H31" s="16">
         <v>32.461846739999999</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="16">
         <v>62.881902920000002</v>
       </c>
-      <c r="J31" s="11"/>
-      <c r="K31" s="19">
+      <c r="J31" s="9"/>
+      <c r="K31" s="17">
         <v>65.027793709999997</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="17">
         <v>57.096257350000002</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
-      <c r="B32" s="16">
+      <c r="A32" s="9"/>
+      <c r="B32" s="14">
         <v>60.349793519999999</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="14">
         <v>78.729445870000006</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="17">
+      <c r="D32" s="9"/>
+      <c r="E32" s="15">
         <v>54.8718</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="15">
         <v>49.8718</v>
       </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="18">
+      <c r="G32" s="9"/>
+      <c r="H32" s="16">
         <v>41.327200650000002</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="16">
         <v>49.07025127</v>
       </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="19">
+      <c r="J32" s="9"/>
+      <c r="K32" s="17">
         <v>53.304503169999997</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="17">
         <v>40.883844549999999</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="16">
+      <c r="A33" s="9"/>
+      <c r="B33" s="14">
         <v>48.890555759999998</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="14">
         <v>16.806543520000002</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="17">
+      <c r="D33" s="9"/>
+      <c r="E33" s="15">
         <v>52.564100000000003</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="15">
         <v>46.025599999999997</v>
       </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="18">
+      <c r="G33" s="9"/>
+      <c r="H33" s="16">
         <v>44.007149929999997</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="16">
         <v>46.449673779999998</v>
       </c>
-      <c r="J33" s="11"/>
-      <c r="K33" s="19">
+      <c r="J33" s="9"/>
+      <c r="K33" s="17">
         <v>52.945178089999999</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="17">
         <v>40.38462569</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="16">
+      <c r="A34" s="9"/>
+      <c r="B34" s="14">
         <v>47.549506350000001</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>17.071404520000002</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="17">
+      <c r="D34" s="9"/>
+      <c r="E34" s="15">
         <v>48.205100000000002</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="15">
         <v>38.333300000000001</v>
       </c>
-      <c r="G34" s="11"/>
-      <c r="H34" s="18">
+      <c r="G34" s="9"/>
+      <c r="H34" s="16">
         <v>44.074060690000003</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="16">
         <v>34.553203889999999</v>
       </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="19">
+      <c r="J34" s="9"/>
+      <c r="K34" s="17">
         <v>45.225738200000002</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="17">
         <v>30.555225920000002</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="16">
+      <c r="A35" s="9"/>
+      <c r="B35" s="14">
         <v>30.889430829999998</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="14">
         <v>26.329037230000001</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="17">
+      <c r="D35" s="9"/>
+      <c r="E35" s="15">
         <v>49.487200000000001</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="15">
         <v>42.179499999999997</v>
       </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="18">
+      <c r="G35" s="9"/>
+      <c r="H35" s="16">
         <v>44.001315239999997</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="16">
         <v>33.90420735</v>
       </c>
-      <c r="J35" s="11"/>
-      <c r="K35" s="19">
+      <c r="J35" s="9"/>
+      <c r="K35" s="17">
         <v>50.843304619999998</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="17">
         <v>37.7446281</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="16">
+      <c r="A36" s="9"/>
+      <c r="B36" s="14">
         <v>28.972835719999999</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="14">
         <v>29.05046892</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="17">
+      <c r="D36" s="9"/>
+      <c r="E36" s="15">
         <v>51.025599999999997</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="15">
         <v>44.102600000000002</v>
       </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="18">
+      <c r="G36" s="9"/>
+      <c r="H36" s="16">
         <v>45.006300449999998</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="16">
         <v>38.299019549999997</v>
       </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="19">
+      <c r="J36" s="9"/>
+      <c r="K36" s="17">
         <v>49.659293939999998</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="17">
         <v>36.27344274</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="16">
+      <c r="A37" s="9"/>
+      <c r="B37" s="14">
         <v>35.16136075</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="14">
         <v>22.786849650000001</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="17">
+      <c r="D37" s="9"/>
+      <c r="E37" s="15">
         <v>45.384599999999999</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="15">
         <v>36.410299999999999</v>
       </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="18">
+      <c r="G37" s="9"/>
+      <c r="H37" s="16">
         <v>44.443840610000002</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="16">
         <v>36.019083299999998</v>
       </c>
-      <c r="J37" s="11"/>
-      <c r="K37" s="19">
+      <c r="J37" s="9"/>
+      <c r="K37" s="17">
         <v>47.142788930000002</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="17">
         <v>32.02506417</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="16">
+      <c r="A38" s="9"/>
+      <c r="B38" s="14">
         <v>45.870369169999996</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="14">
         <v>17.489393369999998</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="17">
+      <c r="D38" s="9"/>
+      <c r="E38" s="15">
         <v>42.820500000000003</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="15">
         <v>32.564100000000003</v>
       </c>
-      <c r="G38" s="11"/>
-      <c r="H38" s="18">
+      <c r="G38" s="9"/>
+      <c r="H38" s="16">
         <v>42.178713399999999</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="16">
         <v>26.492119479999999</v>
       </c>
-      <c r="J38" s="11"/>
-      <c r="K38" s="19">
+      <c r="J38" s="9"/>
+      <c r="K38" s="17">
         <v>41.270056529999998</v>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="17">
         <v>21.72181715</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="16">
+      <c r="A39" s="9"/>
+      <c r="B39" s="14">
         <v>32.831420610000002</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="14">
         <v>24.797538150000001</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="17">
+      <c r="D39" s="9"/>
+      <c r="E39" s="15">
         <v>38.7179</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="15">
         <v>31.410299999999999</v>
       </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="18">
+      <c r="G39" s="9"/>
+      <c r="H39" s="16">
         <v>44.04456562</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="16">
         <v>35.662238279999997</v>
       </c>
-      <c r="J39" s="11"/>
-      <c r="K39" s="19">
+      <c r="J39" s="9"/>
+      <c r="K39" s="17">
         <v>47.130127160000001</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="17">
         <v>31.309902919999999</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
-      <c r="B40" s="16">
+      <c r="A40" s="9"/>
+      <c r="B40" s="14">
         <v>39.485574790000001</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="14">
         <v>20.03305005</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="17">
+      <c r="D40" s="9"/>
+      <c r="E40" s="15">
         <v>35.1282</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="15">
         <v>30.256399999999999</v>
       </c>
-      <c r="G40" s="11"/>
-      <c r="H40" s="18">
+      <c r="G40" s="9"/>
+      <c r="H40" s="16">
         <v>41.64045402</v>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="16">
         <v>27.093095420000001</v>
       </c>
-      <c r="J40" s="11"/>
-      <c r="K40" s="19">
+      <c r="J40" s="9"/>
+      <c r="K40" s="17">
         <v>40.915971579999997</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="17">
         <v>23.541592390000002</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
-      <c r="B41" s="16">
+      <c r="A41" s="9"/>
+      <c r="B41" s="14">
         <v>33.446182929999999</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="14">
         <v>24.19064341</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="17">
+      <c r="D41" s="9"/>
+      <c r="E41" s="15">
         <v>32.564100000000003</v>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="15">
         <v>32.179499999999997</v>
       </c>
-      <c r="G41" s="11"/>
-      <c r="H41" s="18">
+      <c r="G41" s="9"/>
+      <c r="H41" s="16">
         <v>41.938330010000001</v>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="16">
         <v>24.991522979999999</v>
       </c>
-      <c r="J41" s="11"/>
-      <c r="K41" s="19">
+      <c r="J41" s="9"/>
+      <c r="K41" s="17">
         <v>38.660163969999999</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="17">
         <v>21.689549639999999</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
-      <c r="B42" s="16">
+      <c r="A42" s="9"/>
+      <c r="B42" s="14">
         <v>21.863581279999998</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="14">
         <v>46.052593350000002</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="17">
+      <c r="D42" s="9"/>
+      <c r="E42" s="15">
         <v>30</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="15">
         <v>36.794899999999998</v>
       </c>
-      <c r="G42" s="11"/>
-      <c r="H42" s="18">
+      <c r="G42" s="9"/>
+      <c r="H42" s="16">
         <v>44.053927510000001</v>
       </c>
-      <c r="I42" s="18">
+      <c r="I42" s="16">
         <v>33.55639249</v>
       </c>
-      <c r="J42" s="11"/>
-      <c r="K42" s="19">
+      <c r="J42" s="9"/>
+      <c r="K42" s="17">
         <v>42.612550830000004</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="17">
         <v>24.195053770000001</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="16">
+      <c r="A43" s="9"/>
+      <c r="B43" s="14">
         <v>25.16587084</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="14">
         <v>35.76661395</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="17">
+      <c r="D43" s="9"/>
+      <c r="E43" s="15">
         <v>33.589700000000001</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="15">
         <v>41.410299999999999</v>
       </c>
-      <c r="G43" s="11"/>
-      <c r="H43" s="18">
+      <c r="G43" s="9"/>
+      <c r="H43" s="16">
         <v>39.206719329999999</v>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="16">
         <v>51.533715700000002</v>
       </c>
-      <c r="J43" s="11"/>
-      <c r="K43" s="19">
+      <c r="J43" s="9"/>
+      <c r="K43" s="17">
         <v>41.209039500000003</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="17">
         <v>24.128709189999999</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="11"/>
-      <c r="B44" s="16">
+      <c r="A44" s="9"/>
+      <c r="B44" s="14">
         <v>22.95947898</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="14">
         <v>51.287706790000001</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="17">
+      <c r="D44" s="9"/>
+      <c r="E44" s="15">
         <v>36.666699999999999</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="15">
         <v>45.640999999999998</v>
       </c>
-      <c r="G44" s="11"/>
-      <c r="H44" s="18">
+      <c r="G44" s="9"/>
+      <c r="H44" s="16">
         <v>28.704449230000002</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="16">
         <v>61.777525400000002</v>
       </c>
-      <c r="J44" s="11"/>
-      <c r="K44" s="19">
+      <c r="J44" s="9"/>
+      <c r="K44" s="17">
         <v>50.649221150000002</v>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="17">
         <v>37.483790740000003</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="11"/>
-      <c r="B45" s="16">
+      <c r="A45" s="9"/>
+      <c r="B45" s="14">
         <v>25.58605524</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="14">
         <v>60.846583359999997</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="17">
+      <c r="D45" s="9"/>
+      <c r="E45" s="15">
         <v>38.205100000000002</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="15">
         <v>49.102600000000002</v>
       </c>
-      <c r="G45" s="11"/>
-      <c r="H45" s="18">
+      <c r="G45" s="9"/>
+      <c r="H45" s="16">
         <v>31.7086629</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="16">
         <v>58.837754369999999</v>
       </c>
-      <c r="J45" s="11"/>
-      <c r="K45" s="19">
+      <c r="J45" s="9"/>
+      <c r="K45" s="17">
         <v>52.131901939999999</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="17">
         <v>39.364602079999997</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
-      <c r="B46" s="16">
+      <c r="A46" s="9"/>
+      <c r="B46" s="14">
         <v>26.314310070000001</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="14">
         <v>33.2971681</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="17">
+      <c r="D46" s="9"/>
+      <c r="E46" s="15">
         <v>29.743600000000001</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="15">
         <v>36.025599999999997</v>
       </c>
-      <c r="G46" s="11"/>
-      <c r="H46" s="18">
+      <c r="G46" s="9"/>
+      <c r="H46" s="16">
         <v>42.811711469999999</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="16">
         <v>30.020448420000001</v>
       </c>
-      <c r="J46" s="11"/>
-      <c r="K46" s="19">
+      <c r="J46" s="9"/>
+      <c r="K46" s="17">
         <v>39.797271270000003</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="17">
         <v>16.083549649999998</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
-      <c r="B47" s="16">
+      <c r="A47" s="9"/>
+      <c r="B47" s="14">
         <v>33.037301249999999</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="14">
         <v>24.56446249</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="17">
+      <c r="D47" s="9"/>
+      <c r="E47" s="15">
         <v>29.743600000000001</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="15">
         <v>32.179499999999997</v>
       </c>
-      <c r="G47" s="11"/>
-      <c r="H47" s="18">
+      <c r="G47" s="9"/>
+      <c r="H47" s="16">
         <v>43.300614889999999</v>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="16">
         <v>31.5264262</v>
       </c>
-      <c r="J47" s="11"/>
-      <c r="K47" s="19">
+      <c r="J47" s="9"/>
+      <c r="K47" s="17">
         <v>43.549881480000003</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="17">
         <v>24.307210940000001</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
-      <c r="B48" s="16">
+      <c r="A48" s="9"/>
+      <c r="B48" s="14">
         <v>36.468889480000001</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="14">
         <v>21.876114470000001</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="17">
+      <c r="D48" s="9"/>
+      <c r="E48" s="15">
         <v>30</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="15">
         <v>29.102599999999999</v>
       </c>
-      <c r="G48" s="11"/>
-      <c r="H48" s="18">
+      <c r="G48" s="9"/>
+      <c r="H48" s="16">
         <v>40.398632910000003</v>
       </c>
-      <c r="I48" s="18">
+      <c r="I48" s="16">
         <v>16.347008379999998</v>
       </c>
-      <c r="J48" s="11"/>
-      <c r="K48" s="19">
+      <c r="J48" s="9"/>
+      <c r="K48" s="17">
         <v>36.714663340000001</v>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="17">
         <v>17.381809860000001</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
-      <c r="B49" s="16">
+      <c r="A49" s="9"/>
+      <c r="B49" s="14">
         <v>26.513553099999999</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="14">
         <v>32.918749820000002</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="17">
+      <c r="D49" s="9"/>
+      <c r="E49" s="15">
         <v>32.051299999999998</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="15">
         <v>26.794899999999998</v>
       </c>
-      <c r="G49" s="11"/>
-      <c r="H49" s="18">
+      <c r="G49" s="9"/>
+      <c r="H49" s="16">
         <v>40.435691579999997</v>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="16">
         <v>20.232670679999998</v>
       </c>
-      <c r="J49" s="11"/>
-      <c r="K49" s="19">
+      <c r="J49" s="9"/>
+      <c r="K49" s="17">
         <v>37.224610130000002</v>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="17">
         <v>17.980064479999999</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" s="11"/>
-      <c r="B50" s="16">
+      <c r="A50" s="9"/>
+      <c r="B50" s="14">
         <v>36.027091210000002</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="14">
         <v>22.195438540000001</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="17">
+      <c r="D50" s="9"/>
+      <c r="E50" s="15">
         <v>35.897399999999998</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="15">
         <v>25.256399999999999</v>
       </c>
-      <c r="G50" s="11"/>
-      <c r="H50" s="18">
+      <c r="G50" s="9"/>
+      <c r="H50" s="16">
         <v>40.936546669999998</v>
       </c>
-      <c r="I50" s="18">
+      <c r="I50" s="16">
         <v>16.913004839999999</v>
       </c>
-      <c r="J50" s="11"/>
-      <c r="K50" s="19">
+      <c r="J50" s="9"/>
+      <c r="K50" s="17">
         <v>40.512447850000001</v>
       </c>
-      <c r="L50" s="19">
+      <c r="L50" s="17">
         <v>22.96221457</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
-      <c r="B51" s="16">
+      <c r="A51" s="9"/>
+      <c r="B51" s="14">
         <v>42.681040410000001</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="14">
         <v>18.542536200000001</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="17">
+      <c r="D51" s="9"/>
+      <c r="E51" s="15">
         <v>41.025599999999997</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="15">
         <v>25.256399999999999</v>
       </c>
-      <c r="G51" s="11"/>
-      <c r="H51" s="18">
+      <c r="G51" s="9"/>
+      <c r="H51" s="16">
         <v>39.661573670000003</v>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="16">
         <v>15.609355580000001</v>
       </c>
-      <c r="J51" s="11"/>
-      <c r="K51" s="19">
+      <c r="J51" s="9"/>
+      <c r="K51" s="17">
         <v>40.222062790000003</v>
       </c>
-      <c r="L51" s="19">
+      <c r="L51" s="17">
         <v>20.614621700000001</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
-      <c r="B52" s="16">
+      <c r="A52" s="9"/>
+      <c r="B52" s="14">
         <v>45.041077129999998</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="14">
         <v>17.73451773</v>
       </c>
-      <c r="D52" s="11"/>
-      <c r="E52" s="17">
+      <c r="D52" s="9"/>
+      <c r="E52" s="15">
         <v>44.102600000000002</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52" s="15">
         <v>25.640999999999998</v>
       </c>
-      <c r="G52" s="11"/>
-      <c r="H52" s="18">
+      <c r="G52" s="9"/>
+      <c r="H52" s="16">
         <v>40.899259180000001</v>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="16">
         <v>20.798528950000001</v>
       </c>
-      <c r="J52" s="11"/>
-      <c r="K52" s="19">
+      <c r="J52" s="9"/>
+      <c r="K52" s="17">
         <v>44.124961210000002</v>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="17">
         <v>23.366245289999998</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
-      <c r="B53" s="16">
+      <c r="A53" s="9"/>
+      <c r="B53" s="14">
         <v>47.352416460000001</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="14">
         <v>17.134745429999999</v>
       </c>
-      <c r="D53" s="11"/>
-      <c r="E53" s="17">
+      <c r="D53" s="9"/>
+      <c r="E53" s="15">
         <v>47.179499999999997</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="15">
         <v>28.718</v>
       </c>
-      <c r="G53" s="11"/>
-      <c r="H53" s="18">
+      <c r="G53" s="9"/>
+      <c r="H53" s="16">
         <v>41.968616830000002</v>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="16">
         <v>26.497072599999999</v>
       </c>
-      <c r="J53" s="11"/>
-      <c r="K53" s="19">
+      <c r="J53" s="9"/>
+      <c r="K53" s="17">
         <v>42.346261599999998</v>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="17">
         <v>24.558326940000001</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="16">
+      <c r="A54" s="9"/>
+      <c r="B54" s="14">
         <v>53.846194029999999</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="14">
         <v>16.387318100000002</v>
       </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="17">
+      <c r="D54" s="9"/>
+      <c r="E54" s="15">
         <v>49.487200000000001</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="15">
         <v>31.410299999999999</v>
       </c>
-      <c r="G54" s="11"/>
-      <c r="H54" s="18">
+      <c r="G54" s="9"/>
+      <c r="H54" s="16">
         <v>40.38340582</v>
       </c>
-      <c r="I54" s="18">
+      <c r="I54" s="16">
         <v>21.391225519999999</v>
       </c>
-      <c r="J54" s="11"/>
-      <c r="K54" s="19">
+      <c r="J54" s="9"/>
+      <c r="K54" s="17">
         <v>44.189084370000003</v>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="17">
         <v>28.772625470000001</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="16">
+      <c r="A55" s="9"/>
+      <c r="B55" s="14">
         <v>55.12963938</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="14">
         <v>16.35324687</v>
       </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="17">
+      <c r="D55" s="9"/>
+      <c r="E55" s="15">
         <v>51.538499999999999</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55" s="15">
         <v>34.8718</v>
       </c>
-      <c r="G55" s="11"/>
-      <c r="H55" s="18">
+      <c r="G55" s="9"/>
+      <c r="H55" s="16">
         <v>56.53812645</v>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="16">
         <v>32.444245469999998</v>
       </c>
-      <c r="J55" s="11"/>
-      <c r="K55" s="19">
+      <c r="J55" s="9"/>
+      <c r="K55" s="17">
         <v>45.814245309999997</v>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="17">
         <v>31.05697967</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
-      <c r="B56" s="16">
+      <c r="A56" s="9"/>
+      <c r="B56" s="14">
         <v>52.188119960000002</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="14">
         <v>16.418217469999998</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="17">
+      <c r="D56" s="9"/>
+      <c r="E56" s="15">
         <v>53.589700000000001</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56" s="15">
         <v>37.564100000000003</v>
       </c>
-      <c r="G56" s="11"/>
-      <c r="H56" s="18">
+      <c r="G56" s="9"/>
+      <c r="H56" s="16">
         <v>52.970691279999997</v>
       </c>
-      <c r="I56" s="18">
+      <c r="I56" s="16">
         <v>29.040196689999998</v>
       </c>
-      <c r="J56" s="11"/>
-      <c r="K56" s="19">
+      <c r="J56" s="9"/>
+      <c r="K56" s="17">
         <v>46.64311927</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="17">
         <v>31.407219059999999</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" s="11"/>
-      <c r="B57" s="16">
+      <c r="A57" s="9"/>
+      <c r="B57" s="14">
         <v>58.67266308</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="14">
         <v>16.663372429999999</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="17">
+      <c r="D57" s="9"/>
+      <c r="E57" s="15">
         <v>55.1282</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57" s="15">
         <v>40.640999999999998</v>
       </c>
-      <c r="G57" s="11"/>
-      <c r="H57" s="18">
+      <c r="G57" s="9"/>
+      <c r="H57" s="16">
         <v>54.620952590000002</v>
       </c>
-      <c r="I57" s="18">
+      <c r="I57" s="16">
         <v>30.344524450000002</v>
       </c>
-      <c r="J57" s="11"/>
-      <c r="K57" s="19">
+      <c r="J57" s="9"/>
+      <c r="K57" s="17">
         <v>52.1898883</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="17">
         <v>39.367796490000003</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" s="11"/>
-      <c r="B58" s="16">
+      <c r="A58" s="9"/>
+      <c r="B58" s="14">
         <v>82.144311599999995</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="14">
         <v>33.195221869999997</v>
       </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="17">
+      <c r="D58" s="9"/>
+      <c r="E58" s="15">
         <v>56.666699999999999</v>
       </c>
-      <c r="F58" s="17">
+      <c r="F58" s="15">
         <v>42.179499999999997</v>
       </c>
-      <c r="G58" s="11"/>
-      <c r="H58" s="18">
+      <c r="G58" s="9"/>
+      <c r="H58" s="16">
         <v>65.099044390000003</v>
       </c>
-      <c r="I58" s="18">
+      <c r="I58" s="16">
         <v>27.24155756</v>
       </c>
-      <c r="J58" s="11"/>
-      <c r="K58" s="19">
+      <c r="J58" s="9"/>
+      <c r="K58" s="17">
         <v>51.100317359999998</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="17">
         <v>38.095699979999999</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A59" s="11"/>
-      <c r="B59" s="16">
+      <c r="A59" s="9"/>
+      <c r="B59" s="14">
         <v>75.686571139999998</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="14">
         <v>24.741510389999998</v>
       </c>
-      <c r="D59" s="11"/>
-      <c r="E59" s="17">
+      <c r="D59" s="9"/>
+      <c r="E59" s="15">
         <v>59.230800000000002</v>
       </c>
-      <c r="F59" s="17">
+      <c r="F59" s="15">
         <v>44.487200000000001</v>
       </c>
-      <c r="G59" s="11"/>
-      <c r="H59" s="18">
+      <c r="G59" s="9"/>
+      <c r="H59" s="16">
         <v>63.055990909999998</v>
       </c>
-      <c r="I59" s="18">
+      <c r="I59" s="16">
         <v>29.70909567</v>
       </c>
-      <c r="J59" s="11"/>
-      <c r="K59" s="19">
+      <c r="J59" s="9"/>
+      <c r="K59" s="17">
         <v>65.400834149999994</v>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="17">
         <v>42.614032039999998</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
-      <c r="B60" s="16">
+      <c r="A60" s="9"/>
+      <c r="B60" s="14">
         <v>85.344964500000003</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="14">
         <v>52.886419869999997</v>
       </c>
-      <c r="D60" s="11"/>
-      <c r="E60" s="17">
+      <c r="D60" s="9"/>
+      <c r="E60" s="15">
         <v>62.307699999999997</v>
       </c>
-      <c r="F60" s="17">
+      <c r="F60" s="15">
         <v>46.025599999999997</v>
       </c>
-      <c r="G60" s="11"/>
-      <c r="H60" s="18">
+      <c r="G60" s="9"/>
+      <c r="H60" s="16">
         <v>70.960136230000003</v>
       </c>
-      <c r="I60" s="18">
+      <c r="I60" s="16">
         <v>41.259501290000003</v>
       </c>
-      <c r="J60" s="11"/>
-      <c r="K60" s="19">
+      <c r="J60" s="9"/>
+      <c r="K60" s="17">
         <v>64.852039829999995</v>
       </c>
-      <c r="L60" s="19">
+      <c r="L60" s="17">
         <v>43.133734840000002</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A61" s="11"/>
-      <c r="B61" s="16">
+      <c r="A61" s="9"/>
+      <c r="B61" s="14">
         <v>83.844653510000001</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="14">
         <v>58.616060230000002</v>
       </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="17">
+      <c r="D61" s="9"/>
+      <c r="E61" s="15">
         <v>64.871799999999993</v>
       </c>
-      <c r="F61" s="17">
+      <c r="F61" s="15">
         <v>46.794899999999998</v>
       </c>
-      <c r="G61" s="11"/>
-      <c r="H61" s="18">
+      <c r="G61" s="9"/>
+      <c r="H61" s="16">
         <v>69.895819239999994</v>
       </c>
-      <c r="I61" s="18">
+      <c r="I61" s="16">
         <v>43.453759269999999</v>
       </c>
-      <c r="J61" s="11"/>
-      <c r="K61" s="19">
+      <c r="J61" s="9"/>
+      <c r="K61" s="17">
         <v>63.403806009999997</v>
       </c>
-      <c r="L61" s="19">
+      <c r="L61" s="17">
         <v>44.84749369</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="11"/>
-      <c r="B62" s="16">
+      <c r="A62" s="9"/>
+      <c r="B62" s="14">
         <v>85.664760659999999</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="14">
         <v>45.54275277</v>
       </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="17">
+      <c r="D62" s="9"/>
+      <c r="E62" s="15">
         <v>67.948700000000002</v>
       </c>
-      <c r="F62" s="17">
+      <c r="F62" s="15">
         <v>47.948700000000002</v>
       </c>
-      <c r="G62" s="11"/>
-      <c r="H62" s="18">
+      <c r="G62" s="9"/>
+      <c r="H62" s="16">
         <v>70.595892860000006</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="16">
         <v>41.96474387</v>
       </c>
-      <c r="J62" s="11"/>
-      <c r="K62" s="19">
+      <c r="J62" s="9"/>
+      <c r="K62" s="17">
         <v>65.371548869999998</v>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="17">
         <v>42.695971319999998</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="11"/>
-      <c r="B63" s="16">
+      <c r="A63" s="9"/>
+      <c r="B63" s="14">
         <v>77.93100493</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="14">
         <v>68.690061880000002</v>
       </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="17">
+      <c r="D63" s="9"/>
+      <c r="E63" s="15">
         <v>70.512799999999999</v>
       </c>
-      <c r="F63" s="17">
+      <c r="F63" s="15">
         <v>53.718000000000004</v>
       </c>
-      <c r="G63" s="11"/>
-      <c r="H63" s="18">
+      <c r="G63" s="9"/>
+      <c r="H63" s="16">
         <v>69.647021429999995</v>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="16">
         <v>44.044445019999998</v>
       </c>
-      <c r="J63" s="11"/>
-      <c r="K63" s="19">
+      <c r="J63" s="9"/>
+      <c r="K63" s="17">
         <v>61.908039700000003</v>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="17">
         <v>53.190352070000003</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64" s="11"/>
-      <c r="B64" s="16">
+      <c r="A64" s="9"/>
+      <c r="B64" s="14">
         <v>73.031833019999993</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="14">
         <v>73.120574730000001</v>
       </c>
-      <c r="D64" s="11"/>
-      <c r="E64" s="17">
+      <c r="D64" s="9"/>
+      <c r="E64" s="15">
         <v>71.538499999999999</v>
       </c>
-      <c r="F64" s="17">
+      <c r="F64" s="15">
         <v>60.640999999999998</v>
       </c>
-      <c r="G64" s="11"/>
-      <c r="H64" s="18">
+      <c r="G64" s="9"/>
+      <c r="H64" s="16">
         <v>77.392982489999994</v>
       </c>
-      <c r="I64" s="18">
+      <c r="I64" s="16">
         <v>63.371459059999999</v>
       </c>
-      <c r="J64" s="11"/>
-      <c r="K64" s="19">
+      <c r="J64" s="9"/>
+      <c r="K64" s="17">
         <v>71.826652999999993</v>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="17">
         <v>65.686230359999996</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
-      <c r="B65" s="16">
+      <c r="A65" s="9"/>
+      <c r="B65" s="14">
         <v>70.102804500000005</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="14">
         <v>75.683206850000005</v>
       </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="17">
+      <c r="D65" s="9"/>
+      <c r="E65" s="15">
         <v>71.538499999999999</v>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="15">
         <v>64.487200000000001</v>
       </c>
-      <c r="G65" s="11"/>
-      <c r="H65" s="18">
+      <c r="G65" s="9"/>
+      <c r="H65" s="16">
         <v>64.400787190000003</v>
       </c>
-      <c r="I65" s="18">
+      <c r="I65" s="16">
         <v>67.448718450000001</v>
       </c>
-      <c r="J65" s="11"/>
-      <c r="K65" s="19">
+      <c r="J65" s="9"/>
+      <c r="K65" s="17">
         <v>72.65462316</v>
       </c>
-      <c r="L65" s="19">
+      <c r="L65" s="17">
         <v>66.878277609999998</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" s="11"/>
-      <c r="B66" s="16">
+      <c r="A66" s="9"/>
+      <c r="B66" s="14">
         <v>57.144694690000001</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="14">
         <v>79.19410259</v>
       </c>
-      <c r="D66" s="11"/>
-      <c r="E66" s="17">
+      <c r="D66" s="9"/>
+      <c r="E66" s="15">
         <v>69.487200000000001</v>
       </c>
-      <c r="F66" s="17">
+      <c r="F66" s="15">
         <v>69.487200000000001</v>
       </c>
-      <c r="G66" s="11"/>
-      <c r="H66" s="18">
+      <c r="G66" s="9"/>
+      <c r="H66" s="16">
         <v>63.868959830000001</v>
       </c>
-      <c r="I66" s="18">
+      <c r="I66" s="16">
         <v>70.213738829999997</v>
       </c>
-      <c r="J66" s="11"/>
-      <c r="K66" s="19">
+      <c r="J66" s="9"/>
+      <c r="K66" s="17">
         <v>76.888578159999994</v>
       </c>
-      <c r="L66" s="19">
+      <c r="L66" s="17">
         <v>72.165472080000001</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A67" s="11"/>
-      <c r="B67" s="16">
+      <c r="A67" s="9"/>
+      <c r="B67" s="14">
         <v>46.962461990000001</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="14">
         <v>78.666559000000007</v>
       </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="17">
+      <c r="D67" s="9"/>
+      <c r="E67" s="15">
         <v>46.923099999999998</v>
       </c>
-      <c r="F67" s="17">
+      <c r="F67" s="15">
         <v>79.871799999999993</v>
       </c>
-      <c r="G67" s="11"/>
-      <c r="H67" s="18">
+      <c r="G67" s="9"/>
+      <c r="H67" s="16">
         <v>56.594421320000002</v>
       </c>
-      <c r="I67" s="18">
+      <c r="I67" s="16">
         <v>86.927006219999996</v>
       </c>
-      <c r="J67" s="11"/>
-      <c r="K67" s="19">
+      <c r="J67" s="9"/>
+      <c r="K67" s="17">
         <v>43.74461968</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="17">
         <v>71.267961080000006</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="11"/>
-      <c r="B68" s="16">
+      <c r="A68" s="9"/>
+      <c r="B68" s="14">
         <v>50.564933809999999</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="14">
         <v>79.077298549999995</v>
       </c>
-      <c r="D68" s="11"/>
-      <c r="E68" s="17">
+      <c r="D68" s="9"/>
+      <c r="E68" s="15">
         <v>48.205100000000002</v>
       </c>
-      <c r="F68" s="17">
+      <c r="F68" s="15">
         <v>84.102599999999995</v>
       </c>
-      <c r="G68" s="11"/>
-      <c r="H68" s="18">
+      <c r="G68" s="9"/>
+      <c r="H68" s="16">
         <v>56.531337290000003</v>
       </c>
-      <c r="I68" s="18">
+      <c r="I68" s="16">
         <v>87.499811070000007</v>
       </c>
-      <c r="J68" s="11"/>
-      <c r="K68" s="19">
+      <c r="J68" s="9"/>
+      <c r="K68" s="17">
         <v>39.054248440000002</v>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="17">
         <v>83.119020699999993</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="11"/>
-      <c r="B69" s="16">
+      <c r="A69" s="9"/>
+      <c r="B69" s="14">
         <v>53.719676569999997</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="14">
         <v>79.30693617</v>
       </c>
-      <c r="D69" s="11"/>
-      <c r="E69" s="17">
+      <c r="D69" s="9"/>
+      <c r="E69" s="15">
         <v>50</v>
       </c>
-      <c r="F69" s="17">
+      <c r="F69" s="15">
         <v>85.256399999999999</v>
       </c>
-      <c r="G69" s="11"/>
-      <c r="H69" s="18">
+      <c r="G69" s="9"/>
+      <c r="H69" s="16">
         <v>59.652158370000002</v>
       </c>
-      <c r="I69" s="18">
+      <c r="I69" s="16">
         <v>87.809461589999998</v>
       </c>
-      <c r="J69" s="11"/>
-      <c r="K69" s="19">
+      <c r="J69" s="9"/>
+      <c r="K69" s="17">
         <v>39.931674630000003</v>
       </c>
-      <c r="L69" s="19">
+      <c r="L69" s="17">
         <v>79.939188000000001</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
-      <c r="B70" s="16">
+      <c r="A70" s="9"/>
+      <c r="B70" s="14">
         <v>54.200232319999998</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="14">
         <v>79.325002339999998</v>
       </c>
-      <c r="D70" s="11"/>
-      <c r="E70" s="17">
+      <c r="D70" s="9"/>
+      <c r="E70" s="15">
         <v>53.076900000000002</v>
       </c>
-      <c r="F70" s="17">
+      <c r="F70" s="15">
         <v>85.256399999999999</v>
       </c>
-      <c r="G70" s="11"/>
-      <c r="H70" s="18">
+      <c r="G70" s="9"/>
+      <c r="H70" s="16">
         <v>56.6365087</v>
       </c>
-      <c r="I70" s="18">
+      <c r="I70" s="16">
         <v>85.637495560000005</v>
       </c>
-      <c r="J70" s="11"/>
-      <c r="K70" s="19">
+      <c r="J70" s="9"/>
+      <c r="K70" s="17">
         <v>39.762826109999999</v>
       </c>
-      <c r="L70" s="19">
+      <c r="L70" s="17">
         <v>76.405967450000006</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="16">
+      <c r="A71" s="9"/>
+      <c r="B71" s="14">
         <v>47.875198339999997</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="14">
         <v>78.675853430000004</v>
       </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="17">
+      <c r="D71" s="9"/>
+      <c r="E71" s="15">
         <v>55.384599999999999</v>
       </c>
-      <c r="F71" s="17">
+      <c r="F71" s="15">
         <v>86.025599999999997</v>
       </c>
-      <c r="G71" s="11"/>
-      <c r="H71" s="18">
+      <c r="G71" s="9"/>
+      <c r="H71" s="16">
         <v>58.672288000000002</v>
       </c>
-      <c r="I71" s="18">
+      <c r="I71" s="16">
         <v>90.077160309999996</v>
       </c>
-      <c r="J71" s="11"/>
-      <c r="K71" s="19">
+      <c r="J71" s="9"/>
+      <c r="K71" s="17">
         <v>41.323383290000002</v>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="17">
         <v>80.211868600000003</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
-      <c r="B72" s="16">
+      <c r="A72" s="9"/>
+      <c r="B72" s="14">
         <v>51.47345851</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="14">
         <v>79.159867000000006</v>
       </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="17">
+      <c r="D72" s="9"/>
+      <c r="E72" s="15">
         <v>56.666699999999999</v>
       </c>
-      <c r="F72" s="17">
+      <c r="F72" s="15">
         <v>86.025599999999997</v>
       </c>
-      <c r="G72" s="11"/>
-      <c r="H72" s="18">
+      <c r="G72" s="9"/>
+      <c r="H72" s="16">
         <v>58.221612729999997</v>
       </c>
-      <c r="I72" s="18">
+      <c r="I72" s="16">
         <v>90.411018769999998</v>
       </c>
-      <c r="J72" s="11"/>
-      <c r="K72" s="19">
+      <c r="J72" s="9"/>
+      <c r="K72" s="17">
         <v>41.787323229999998</v>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="17">
         <v>83.988077989999994</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A73" s="11"/>
-      <c r="B73" s="16">
+      <c r="A73" s="9"/>
+      <c r="B73" s="14">
         <v>52.751222220000002</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="14">
         <v>79.293659930000004</v>
       </c>
-      <c r="D73" s="11"/>
-      <c r="E73" s="17">
+      <c r="D73" s="9"/>
+      <c r="E73" s="15">
         <v>56.153799999999997</v>
       </c>
-      <c r="F73" s="17">
+      <c r="F73" s="15">
         <v>82.948700000000002</v>
       </c>
-      <c r="G73" s="11"/>
-      <c r="H73" s="18">
+      <c r="G73" s="9"/>
+      <c r="H73" s="16">
         <v>57.914664479999999</v>
       </c>
-      <c r="I73" s="18">
+      <c r="I73" s="16">
         <v>89.953802769999996</v>
       </c>
-      <c r="J73" s="11"/>
-      <c r="K73" s="19">
+      <c r="J73" s="9"/>
+      <c r="K73" s="17">
         <v>39.755649069999997</v>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="17">
         <v>79.657096640000006</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
-      <c r="B74" s="16">
+      <c r="A74" s="9"/>
+      <c r="B74" s="14">
         <v>48.562223000000003</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="14">
         <v>78.782383530000004</v>
       </c>
-      <c r="D74" s="11"/>
-      <c r="E74" s="17">
+      <c r="D74" s="9"/>
+      <c r="E74" s="15">
         <v>53.846200000000003</v>
       </c>
-      <c r="F74" s="17">
+      <c r="F74" s="15">
         <v>80.641000000000005</v>
       </c>
-      <c r="G74" s="11"/>
-      <c r="H74" s="18">
+      <c r="G74" s="9"/>
+      <c r="H74" s="16">
         <v>55.315509059999997</v>
       </c>
-      <c r="I74" s="18">
+      <c r="I74" s="16">
         <v>80.251860690000001</v>
       </c>
-      <c r="J74" s="11"/>
-      <c r="K74" s="19">
+      <c r="J74" s="9"/>
+      <c r="K74" s="17">
         <v>40.749879399999998</v>
       </c>
-      <c r="L74" s="19">
+      <c r="L74" s="17">
         <v>77.20465729</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
-      <c r="B75" s="16">
+      <c r="A75" s="9"/>
+      <c r="B75" s="14">
         <v>53.081241689999999</v>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="14">
         <v>79.297250770000005</v>
       </c>
-      <c r="D75" s="11"/>
-      <c r="E75" s="17">
+      <c r="D75" s="9"/>
+      <c r="E75" s="15">
         <v>51.2821</v>
       </c>
-      <c r="F75" s="17">
+      <c r="F75" s="15">
         <v>78.718000000000004</v>
       </c>
-      <c r="G75" s="11"/>
-      <c r="H75" s="18">
+      <c r="G75" s="9"/>
+      <c r="H75" s="16">
         <v>54.575728589999997</v>
       </c>
-      <c r="I75" s="18">
+      <c r="I75" s="16">
         <v>77.536288470000002</v>
       </c>
-      <c r="J75" s="11"/>
-      <c r="K75" s="19">
+      <c r="J75" s="9"/>
+      <c r="K75" s="17">
         <v>43.8568985</v>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="17">
         <v>77.609843650000002</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="B76" s="16">
+      <c r="A76" s="9"/>
+      <c r="B76" s="14">
         <v>56.475383370000003</v>
       </c>
-      <c r="C76" s="16">
+      <c r="C76" s="14">
         <v>79.167840100000006</v>
       </c>
-      <c r="D76" s="11"/>
-      <c r="E76" s="17">
+      <c r="D76" s="9"/>
+      <c r="E76" s="15">
         <v>50</v>
       </c>
-      <c r="F76" s="17">
+      <c r="F76" s="15">
         <v>78.718000000000004</v>
       </c>
-      <c r="G76" s="11"/>
-      <c r="H76" s="18">
+      <c r="G76" s="9"/>
+      <c r="H76" s="16">
         <v>54.41309365</v>
       </c>
-      <c r="I76" s="18">
+      <c r="I76" s="16">
         <v>78.229086589999994</v>
       </c>
-      <c r="J76" s="11"/>
-      <c r="K76" s="19">
+      <c r="J76" s="9"/>
+      <c r="K76" s="17">
         <v>42.367822500000003</v>
       </c>
-      <c r="L76" s="19">
+      <c r="L76" s="17">
         <v>73.638271829999994</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A77" s="11"/>
-      <c r="B77" s="16">
+      <c r="A77" s="9"/>
+      <c r="B77" s="14">
         <v>49.570911410000001</v>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="14">
         <v>79.038123880000001</v>
       </c>
-      <c r="D77" s="11"/>
-      <c r="E77" s="17">
+      <c r="D77" s="9"/>
+      <c r="E77" s="15">
         <v>47.948700000000002</v>
       </c>
-      <c r="F77" s="17">
+      <c r="F77" s="15">
         <v>77.564099999999996</v>
       </c>
-      <c r="G77" s="11"/>
-      <c r="H77" s="18">
+      <c r="G77" s="9"/>
+      <c r="H77" s="16">
         <v>55.074505899999998</v>
       </c>
-      <c r="I77" s="18">
+      <c r="I77" s="16">
         <v>79.817546419999999</v>
       </c>
-      <c r="J77" s="11"/>
-      <c r="K77" s="19">
+      <c r="J77" s="9"/>
+      <c r="K77" s="17">
         <v>39.462959840000003</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="17">
         <v>78.459973899999994</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
-      <c r="B78" s="16">
+      <c r="A78" s="9"/>
+      <c r="B78" s="14">
         <v>37.6277033</v>
       </c>
-      <c r="C78" s="16">
+      <c r="C78" s="14">
         <v>74.557504339999994</v>
       </c>
-      <c r="D78" s="11"/>
-      <c r="E78" s="17">
+      <c r="D78" s="9"/>
+      <c r="E78" s="15">
         <v>29.743600000000001</v>
       </c>
-      <c r="F78" s="17">
+      <c r="F78" s="15">
         <v>59.8718</v>
       </c>
-      <c r="G78" s="11"/>
-      <c r="H78" s="18">
+      <c r="G78" s="9"/>
+      <c r="H78" s="16">
         <v>29.432960520000002</v>
       </c>
-      <c r="I78" s="18">
+      <c r="I78" s="16">
         <v>60.801776539999999</v>
       </c>
-      <c r="J78" s="11"/>
-      <c r="K78" s="19">
+      <c r="J78" s="9"/>
+      <c r="K78" s="17">
         <v>44.517333950000001</v>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="17">
         <v>70.369349830000004</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" s="11"/>
-      <c r="B79" s="16">
+      <c r="A79" s="9"/>
+      <c r="B79" s="14">
         <v>32.26370009</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="14">
         <v>70.316638900000001</v>
       </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="17">
+      <c r="D79" s="9"/>
+      <c r="E79" s="15">
         <v>29.743600000000001</v>
       </c>
-      <c r="F79" s="17">
+      <c r="F79" s="15">
         <v>62.179499999999997</v>
       </c>
-      <c r="G79" s="11"/>
-      <c r="H79" s="18">
+      <c r="G79" s="9"/>
+      <c r="H79" s="16">
         <v>29.422686070000001</v>
       </c>
-      <c r="I79" s="18">
+      <c r="I79" s="16">
         <v>63.068464820000003</v>
       </c>
-      <c r="J79" s="11"/>
-      <c r="K79" s="19">
+      <c r="J79" s="9"/>
+      <c r="K79" s="17">
         <v>41.636093000000002</v>
       </c>
-      <c r="L79" s="19">
+      <c r="L79" s="17">
         <v>76.249222919999994</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A80" s="11"/>
-      <c r="B80" s="16">
+      <c r="A80" s="9"/>
+      <c r="B80" s="14">
         <v>32.542380340000001</v>
       </c>
-      <c r="C80" s="16">
+      <c r="C80" s="14">
         <v>70.702417209999993</v>
       </c>
-      <c r="D80" s="11"/>
-      <c r="E80" s="17">
+      <c r="D80" s="9"/>
+      <c r="E80" s="15">
         <v>31.2821</v>
       </c>
-      <c r="F80" s="17">
+      <c r="F80" s="15">
         <v>62.564100000000003</v>
       </c>
-      <c r="G80" s="11"/>
-      <c r="H80" s="18">
+      <c r="G80" s="9"/>
+      <c r="H80" s="16">
         <v>29.00561416</v>
       </c>
-      <c r="I80" s="18">
+      <c r="I80" s="16">
         <v>63.390751330000001</v>
       </c>
-      <c r="J80" s="11"/>
-      <c r="K80" s="19">
+      <c r="J80" s="9"/>
+      <c r="K80" s="17">
         <v>45.422932179999997</v>
       </c>
-      <c r="L80" s="19">
+      <c r="L80" s="17">
         <v>69.095501670000004</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A81" s="11"/>
-      <c r="B81" s="16">
+      <c r="A81" s="9"/>
+      <c r="B81" s="14">
         <v>52.825017189999997</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="14">
         <v>85.578133879999996</v>
       </c>
-      <c r="D81" s="11"/>
-      <c r="E81" s="17">
+      <c r="D81" s="9"/>
+      <c r="E81" s="15">
         <v>57.948700000000002</v>
       </c>
-      <c r="F81" s="17">
+      <c r="F81" s="15">
         <v>99.487200000000001</v>
       </c>
-      <c r="G81" s="11"/>
-      <c r="H81" s="18">
+      <c r="G81" s="9"/>
+      <c r="H81" s="16">
         <v>58.461838589999999</v>
       </c>
-      <c r="I81" s="18">
+      <c r="I81" s="16">
         <v>90.265326389999998</v>
       </c>
-      <c r="J81" s="11"/>
-      <c r="K81" s="19">
+      <c r="J81" s="9"/>
+      <c r="K81" s="17">
         <v>42.002856270000002</v>
       </c>
-      <c r="L81" s="19">
+      <c r="L81" s="17">
         <v>97.837614720000005</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A82" s="11"/>
-      <c r="B82" s="16">
+      <c r="A82" s="9"/>
+      <c r="B82" s="14">
         <v>58.528289540000003</v>
       </c>
-      <c r="C82" s="16">
+      <c r="C82" s="14">
         <v>78.978704250000007</v>
       </c>
-      <c r="D82" s="11"/>
-      <c r="E82" s="17">
+      <c r="D82" s="9"/>
+      <c r="E82" s="15">
         <v>61.794899999999998</v>
       </c>
-      <c r="F82" s="17">
+      <c r="F82" s="15">
         <v>99.102599999999995</v>
       </c>
-      <c r="G82" s="11"/>
-      <c r="H82" s="18">
+      <c r="G82" s="9"/>
+      <c r="H82" s="16">
         <v>57.997804739999999</v>
       </c>
-      <c r="I82" s="18">
+      <c r="I82" s="16">
         <v>92.159908610000002</v>
       </c>
-      <c r="J82" s="11"/>
-      <c r="K82" s="19">
+      <c r="J82" s="9"/>
+      <c r="K82" s="17">
         <v>76.105629030000003</v>
       </c>
-      <c r="L82" s="19">
+      <c r="L82" s="17">
         <v>95.304980580000006</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A83" s="11"/>
-      <c r="B83" s="16">
+      <c r="A83" s="9"/>
+      <c r="B83" s="14">
         <v>56.265834259999998</v>
       </c>
-      <c r="C83" s="16">
+      <c r="C83" s="14">
         <v>79.252939490000003</v>
       </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="17">
+      <c r="D83" s="9"/>
+      <c r="E83" s="15">
         <v>64.871799999999993</v>
       </c>
-      <c r="F83" s="17">
+      <c r="F83" s="15">
         <v>97.564099999999996</v>
       </c>
-      <c r="G83" s="11"/>
-      <c r="H83" s="18">
+      <c r="G83" s="9"/>
+      <c r="H83" s="16">
         <v>57.549474080000003</v>
       </c>
-      <c r="I83" s="18">
+      <c r="I83" s="16">
         <v>90.748906559999995</v>
       </c>
-      <c r="J83" s="11"/>
-      <c r="K83" s="19">
+      <c r="J83" s="9"/>
+      <c r="K83" s="17">
         <v>79.20256268</v>
       </c>
-      <c r="L83" s="19">
+      <c r="L83" s="17">
         <v>92.407215629999996</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A84" s="11"/>
-      <c r="B84" s="16">
+      <c r="A84" s="9"/>
+      <c r="B84" s="14">
         <v>57.075892420000002</v>
       </c>
-      <c r="C84" s="16">
+      <c r="C84" s="14">
         <v>79.193922540000003</v>
       </c>
-      <c r="D84" s="11"/>
-      <c r="E84" s="17">
+      <c r="D84" s="9"/>
+      <c r="E84" s="15">
         <v>68.461500000000001</v>
       </c>
-      <c r="F84" s="17">
+      <c r="F84" s="15">
         <v>94.102599999999995</v>
       </c>
-      <c r="G84" s="11"/>
-      <c r="H84" s="18">
+      <c r="G84" s="9"/>
+      <c r="H84" s="16">
         <v>59.529928460000001</v>
       </c>
-      <c r="I84" s="18">
+      <c r="I84" s="16">
         <v>88.327274149999994</v>
       </c>
-      <c r="J84" s="11"/>
-      <c r="K84" s="19">
+      <c r="J84" s="9"/>
+      <c r="K84" s="17">
         <v>84.848244089999994</v>
       </c>
-      <c r="L84" s="19">
+      <c r="L84" s="17">
         <v>95.424804530000003</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A85" s="11"/>
-      <c r="B85" s="16">
+      <c r="A85" s="9"/>
+      <c r="B85" s="14">
         <v>54.256402379999997</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="14">
         <v>79.313864850000002</v>
       </c>
-      <c r="D85" s="11"/>
-      <c r="E85" s="17">
+      <c r="D85" s="9"/>
+      <c r="E85" s="15">
         <v>70.769199999999998</v>
       </c>
-      <c r="F85" s="17">
+      <c r="F85" s="15">
         <v>91.025599999999997</v>
       </c>
-      <c r="G85" s="11"/>
-      <c r="H85" s="18">
+      <c r="G85" s="9"/>
+      <c r="H85" s="16">
         <v>58.249391060000001</v>
       </c>
-      <c r="I85" s="18">
+      <c r="I85" s="16">
         <v>92.129681480000002</v>
       </c>
-      <c r="J85" s="11"/>
-      <c r="K85" s="19">
+      <c r="J85" s="9"/>
+      <c r="K85" s="17">
         <v>81.56447532</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="17">
         <v>83.792907229999997</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A86" s="11"/>
-      <c r="B86" s="16">
+      <c r="A86" s="9"/>
+      <c r="B86" s="14">
         <v>62.685671249999999</v>
       </c>
-      <c r="C86" s="16">
+      <c r="C86" s="14">
         <v>78.174743269999993</v>
       </c>
-      <c r="D86" s="11"/>
-      <c r="E86" s="17">
+      <c r="D86" s="9"/>
+      <c r="E86" s="15">
         <v>72.051299999999998</v>
       </c>
-      <c r="F86" s="17">
+      <c r="F86" s="15">
         <v>86.410300000000007</v>
       </c>
-      <c r="G86" s="11"/>
-      <c r="H86" s="18">
+      <c r="G86" s="9"/>
+      <c r="H86" s="16">
         <v>58.024514009999997</v>
       </c>
-      <c r="I86" s="18">
+      <c r="I86" s="16">
         <v>91.694421169999998</v>
       </c>
-      <c r="J86" s="11"/>
-      <c r="K86" s="19">
+      <c r="J86" s="9"/>
+      <c r="K86" s="17">
         <v>85.446186400000002</v>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="17">
         <v>83.078293840000001</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A87" s="11"/>
-      <c r="B87" s="16">
+      <c r="A87" s="9"/>
+      <c r="B87" s="14">
         <v>68.085605860000001</v>
       </c>
-      <c r="C87" s="16">
+      <c r="C87" s="14">
         <v>76.112317500000003</v>
       </c>
-      <c r="D87" s="11"/>
-      <c r="E87" s="17">
+      <c r="D87" s="9"/>
+      <c r="E87" s="15">
         <v>73.846199999999996</v>
       </c>
-      <c r="F87" s="17">
+      <c r="F87" s="15">
         <v>83.333299999999994</v>
       </c>
-      <c r="G87" s="11"/>
-      <c r="H87" s="18">
+      <c r="G87" s="9"/>
+      <c r="H87" s="16">
         <v>58.382124490000002</v>
       </c>
-      <c r="I87" s="18">
+      <c r="I87" s="16">
         <v>90.553476070000002</v>
       </c>
-      <c r="J87" s="11"/>
-      <c r="K87" s="19">
+      <c r="J87" s="9"/>
+      <c r="K87" s="17">
         <v>80.312491379999997</v>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="17">
         <v>76.516238950000002</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A88" s="11"/>
-      <c r="B88" s="16">
+      <c r="A88" s="9"/>
+      <c r="B88" s="14">
         <v>65.118121959999996</v>
       </c>
-      <c r="C88" s="16">
+      <c r="C88" s="14">
         <v>77.399188449999997</v>
       </c>
-      <c r="D88" s="11"/>
-      <c r="E88" s="17">
+      <c r="D88" s="9"/>
+      <c r="E88" s="15">
         <v>75.128200000000007</v>
       </c>
-      <c r="F88" s="17">
+      <c r="F88" s="15">
         <v>79.102599999999995</v>
       </c>
-      <c r="G88" s="11"/>
-      <c r="H88" s="18">
+      <c r="G88" s="9"/>
+      <c r="H88" s="16">
         <v>62.566759040000001</v>
       </c>
-      <c r="I88" s="18">
+      <c r="I88" s="16">
         <v>77.743934760000002</v>
       </c>
-      <c r="J88" s="11"/>
-      <c r="K88" s="19">
+      <c r="J88" s="9"/>
+      <c r="K88" s="17">
         <v>80.766232299999999</v>
       </c>
-      <c r="L88" s="19">
+      <c r="L88" s="17">
         <v>79.896065680000007</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A89" s="11"/>
-      <c r="B89" s="16">
+      <c r="A89" s="9"/>
+      <c r="B89" s="14">
         <v>68.745631299999999</v>
       </c>
-      <c r="C89" s="16">
+      <c r="C89" s="14">
         <v>75.790055449999997</v>
       </c>
-      <c r="D89" s="11"/>
-      <c r="E89" s="17">
+      <c r="D89" s="9"/>
+      <c r="E89" s="15">
         <v>76.666700000000006</v>
       </c>
-      <c r="F89" s="17">
+      <c r="F89" s="15">
         <v>75.256399999999999</v>
       </c>
-      <c r="G89" s="11"/>
-      <c r="H89" s="18">
+      <c r="G89" s="9"/>
+      <c r="H89" s="16">
         <v>72.175824309999996</v>
       </c>
-      <c r="I89" s="18">
+      <c r="I89" s="16">
         <v>63.128929419999999</v>
       </c>
-      <c r="J89" s="11"/>
-      <c r="K89" s="19">
+      <c r="J89" s="9"/>
+      <c r="K89" s="17">
         <v>82.67011248</v>
       </c>
-      <c r="L89" s="19">
+      <c r="L89" s="17">
         <v>81.711479850000003</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A90" s="11"/>
-      <c r="B90" s="16">
+      <c r="A90" s="9"/>
+      <c r="B90" s="14">
         <v>63.090225140000001</v>
       </c>
-      <c r="C90" s="16">
+      <c r="C90" s="14">
         <v>78.0414095</v>
       </c>
-      <c r="D90" s="11"/>
-      <c r="E90" s="17">
+      <c r="D90" s="9"/>
+      <c r="E90" s="15">
         <v>77.692300000000003</v>
       </c>
-      <c r="F90" s="17">
+      <c r="F90" s="15">
         <v>71.410300000000007</v>
       </c>
-      <c r="G90" s="11"/>
-      <c r="H90" s="18">
+      <c r="G90" s="9"/>
+      <c r="H90" s="16">
         <v>79.472761570000003</v>
       </c>
-      <c r="I90" s="18">
+      <c r="I90" s="16">
         <v>63.408686119999999</v>
       </c>
-      <c r="J90" s="11"/>
-      <c r="K90" s="19">
+      <c r="J90" s="9"/>
+      <c r="K90" s="17">
         <v>77.163625479999993</v>
       </c>
-      <c r="L90" s="19">
+      <c r="L90" s="17">
         <v>73.523718959999997</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A91" s="11"/>
-      <c r="B91" s="16">
+      <c r="A91" s="9"/>
+      <c r="B91" s="14">
         <v>77.204589319999997</v>
       </c>
-      <c r="C91" s="16">
+      <c r="C91" s="14">
         <v>69.312149770000005</v>
       </c>
-      <c r="D91" s="11"/>
-      <c r="E91" s="17">
+      <c r="D91" s="9"/>
+      <c r="E91" s="15">
         <v>79.743600000000001</v>
       </c>
-      <c r="F91" s="17">
+      <c r="F91" s="15">
         <v>66.794899999999998</v>
       </c>
-      <c r="G91" s="11"/>
-      <c r="H91" s="18">
+      <c r="G91" s="9"/>
+      <c r="H91" s="16">
         <v>80.357700879999996</v>
       </c>
-      <c r="I91" s="18">
+      <c r="I91" s="16">
         <v>63.295437540000002</v>
       </c>
-      <c r="J91" s="11"/>
-      <c r="K91" s="19">
+      <c r="J91" s="9"/>
+      <c r="K91" s="17">
         <v>74.070700029999998</v>
       </c>
-      <c r="L91" s="19">
+      <c r="L91" s="17">
         <v>68.479564289999999</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A92" s="11"/>
-      <c r="B92" s="16">
+      <c r="A92" s="9"/>
+      <c r="B92" s="14">
         <v>82.033908479999994</v>
       </c>
-      <c r="C92" s="16">
+      <c r="C92" s="14">
         <v>62.68186979</v>
       </c>
-      <c r="D92" s="11"/>
-      <c r="E92" s="17">
+      <c r="D92" s="9"/>
+      <c r="E92" s="15">
         <v>81.794899999999998</v>
       </c>
-      <c r="F92" s="17">
+      <c r="F92" s="15">
         <v>60.256399999999999</v>
       </c>
-      <c r="G92" s="11"/>
-      <c r="H92" s="18">
+      <c r="G92" s="9"/>
+      <c r="H92" s="16">
         <v>78.757236140000003</v>
       </c>
-      <c r="I92" s="18">
+      <c r="I92" s="16">
         <v>53.332620009999999</v>
       </c>
-      <c r="J92" s="11"/>
-      <c r="K92" s="19">
+      <c r="J92" s="9"/>
+      <c r="K92" s="17">
         <v>74.11423087</v>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="17">
         <v>71.926363519999995</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A93" s="11"/>
-      <c r="B93" s="16">
+      <c r="A93" s="9"/>
+      <c r="B93" s="14">
         <v>81.577945920000005</v>
       </c>
-      <c r="C93" s="16">
+      <c r="C93" s="14">
         <v>63.894925499999999</v>
       </c>
-      <c r="D93" s="11"/>
-      <c r="E93" s="17">
+      <c r="D93" s="9"/>
+      <c r="E93" s="15">
         <v>83.333299999999994</v>
       </c>
-      <c r="F93" s="17">
+      <c r="F93" s="15">
         <v>55.256399999999999</v>
       </c>
-      <c r="G93" s="11"/>
-      <c r="H93" s="18">
+      <c r="G93" s="9"/>
+      <c r="H93" s="16">
         <v>82.540239589999999</v>
       </c>
-      <c r="I93" s="18">
+      <c r="I93" s="16">
         <v>56.541052290000003</v>
       </c>
-      <c r="J93" s="11"/>
-      <c r="K93" s="19">
+      <c r="J93" s="9"/>
+      <c r="K93" s="17">
         <v>68.942075459999998</v>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="17">
         <v>62.635150580000001</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A94" s="11"/>
-      <c r="B94" s="16">
+      <c r="A94" s="9"/>
+      <c r="B94" s="14">
         <v>85.180143279999996</v>
       </c>
-      <c r="C94" s="16">
+      <c r="C94" s="14">
         <v>53.781676660000002</v>
       </c>
-      <c r="D94" s="11"/>
-      <c r="E94" s="17">
+      <c r="D94" s="9"/>
+      <c r="E94" s="15">
         <v>85.128200000000007</v>
       </c>
-      <c r="F94" s="17">
+      <c r="F94" s="15">
         <v>51.410299999999999</v>
       </c>
-      <c r="G94" s="11"/>
-      <c r="H94" s="18">
+      <c r="G94" s="9"/>
+      <c r="H94" s="16">
         <v>86.435897190000006</v>
       </c>
-      <c r="I94" s="18">
+      <c r="I94" s="16">
         <v>59.792761810000002</v>
       </c>
-      <c r="J94" s="11"/>
-      <c r="K94" s="19">
+      <c r="J94" s="9"/>
+      <c r="K94" s="17">
         <v>73.242002330000005</v>
       </c>
-      <c r="L94" s="19">
+      <c r="L94" s="17">
         <v>67.353271129999996</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" s="11"/>
-      <c r="B95" s="16">
+      <c r="A95" s="9"/>
+      <c r="B95" s="14">
         <v>84.28682499</v>
       </c>
-      <c r="C95" s="16">
+      <c r="C95" s="14">
         <v>57.256168090000003</v>
       </c>
-      <c r="D95" s="11"/>
-      <c r="E95" s="17">
+      <c r="D95" s="9"/>
+      <c r="E95" s="15">
         <v>86.410300000000007</v>
       </c>
-      <c r="F95" s="17">
+      <c r="F95" s="15">
         <v>47.564100000000003</v>
       </c>
-      <c r="G95" s="11"/>
-      <c r="H95" s="18">
+      <c r="G95" s="9"/>
+      <c r="H95" s="16">
         <v>79.488684419999998</v>
       </c>
-      <c r="I95" s="18">
+      <c r="I95" s="16">
         <v>53.65167426</v>
       </c>
-      <c r="J95" s="11"/>
-      <c r="K95" s="19">
+      <c r="J95" s="9"/>
+      <c r="K95" s="17">
         <v>71.867013159999999</v>
       </c>
-      <c r="L95" s="19">
+      <c r="L95" s="17">
         <v>34.329157590000001</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A96" s="11"/>
-      <c r="B96" s="16">
+      <c r="A96" s="9"/>
+      <c r="B96" s="14">
         <v>85.622486710000004</v>
       </c>
-      <c r="C96" s="16">
+      <c r="C96" s="14">
         <v>45.024165859999997</v>
       </c>
-      <c r="D96" s="11"/>
-      <c r="E96" s="17">
+      <c r="D96" s="9"/>
+      <c r="E96" s="15">
         <v>87.948700000000002</v>
       </c>
-      <c r="F96" s="17">
+      <c r="F96" s="15">
         <v>46.025599999999997</v>
       </c>
-      <c r="G96" s="11"/>
-      <c r="H96" s="18">
+      <c r="G96" s="9"/>
+      <c r="H96" s="16">
         <v>81.530420320000005</v>
       </c>
-      <c r="I96" s="18">
+      <c r="I96" s="16">
         <v>56.025364570000001</v>
       </c>
-      <c r="J96" s="11"/>
-      <c r="K96" s="19">
+      <c r="J96" s="9"/>
+      <c r="K96" s="17">
         <v>71.569188850000003</v>
       </c>
-      <c r="L96" s="19">
+      <c r="L96" s="17">
         <v>34.699218610000003</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="11"/>
-      <c r="B97" s="16">
+      <c r="A97" s="9"/>
+      <c r="B97" s="14">
         <v>85.604499020000006</v>
       </c>
-      <c r="C97" s="16">
+      <c r="C97" s="14">
         <v>50.762337909999999</v>
       </c>
-      <c r="D97" s="11"/>
-      <c r="E97" s="17">
+      <c r="D97" s="9"/>
+      <c r="E97" s="15">
         <v>89.487200000000001</v>
       </c>
-      <c r="F97" s="17">
+      <c r="F97" s="15">
         <v>42.564100000000003</v>
       </c>
-      <c r="G97" s="11"/>
-      <c r="H97" s="18">
+      <c r="G97" s="9"/>
+      <c r="H97" s="16">
         <v>79.186788570000004</v>
       </c>
-      <c r="I97" s="18">
+      <c r="I97" s="16">
         <v>53.234791850000001</v>
       </c>
-      <c r="J97" s="11"/>
-      <c r="K97" s="19">
+      <c r="J97" s="9"/>
+      <c r="K97" s="17">
         <v>71.48290969</v>
       </c>
-      <c r="L97" s="19">
+      <c r="L97" s="17">
         <v>34.680516990000001</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A98" s="11"/>
-      <c r="B98" s="16">
+      <c r="A98" s="9"/>
+      <c r="B98" s="14">
         <v>84.424785830000005</v>
       </c>
-      <c r="C98" s="16">
+      <c r="C98" s="14">
         <v>38.761410159999997</v>
       </c>
-      <c r="D98" s="11"/>
-      <c r="E98" s="17">
+      <c r="D98" s="9"/>
+      <c r="E98" s="15">
         <v>93.333299999999994</v>
       </c>
-      <c r="F98" s="17">
+      <c r="F98" s="15">
         <v>39.8718</v>
       </c>
-      <c r="G98" s="11"/>
-      <c r="H98" s="18">
+      <c r="G98" s="9"/>
+      <c r="H98" s="16">
         <v>77.89905795</v>
       </c>
-      <c r="I98" s="18">
+      <c r="I98" s="16">
         <v>51.822458330000003</v>
       </c>
-      <c r="J98" s="11"/>
-      <c r="K98" s="19">
+      <c r="J98" s="9"/>
+      <c r="K98" s="17">
         <v>78.128522050000001</v>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="17">
         <v>23.139231840000001</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A99" s="11"/>
-      <c r="B99" s="16">
+      <c r="A99" s="9"/>
+      <c r="B99" s="14">
         <v>85.57098508</v>
       </c>
-      <c r="C99" s="16">
+      <c r="C99" s="14">
         <v>44.560096440000002</v>
       </c>
-      <c r="D99" s="11"/>
-      <c r="E99" s="17">
+      <c r="D99" s="9"/>
+      <c r="E99" s="15">
         <v>95.384600000000006</v>
       </c>
-      <c r="F99" s="17">
+      <c r="F99" s="15">
         <v>36.794899999999998</v>
       </c>
-      <c r="G99" s="11"/>
-      <c r="H99" s="18">
+      <c r="G99" s="9"/>
+      <c r="H99" s="16">
         <v>75.130714209999994</v>
       </c>
-      <c r="I99" s="18">
+      <c r="I99" s="16">
         <v>23.372441970000001</v>
       </c>
-      <c r="J99" s="11"/>
-      <c r="K99" s="19">
+      <c r="J99" s="9"/>
+      <c r="K99" s="17">
         <v>78.789825250000007</v>
       </c>
-      <c r="L99" s="19">
+      <c r="L99" s="17">
         <v>25.597193350000001</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A100" s="11"/>
-      <c r="B100" s="16">
+      <c r="A100" s="9"/>
+      <c r="B100" s="14">
         <v>84.626724199999998</v>
       </c>
-      <c r="C100" s="16">
+      <c r="C100" s="14">
         <v>39.487077509999999</v>
       </c>
-      <c r="D100" s="11"/>
-      <c r="E100" s="17">
+      <c r="D100" s="9"/>
+      <c r="E100" s="15">
         <v>98.205100000000002</v>
       </c>
-      <c r="F100" s="17">
+      <c r="F100" s="15">
         <v>33.718000000000004</v>
       </c>
-      <c r="G100" s="11"/>
-      <c r="H100" s="18">
+      <c r="G100" s="9"/>
+      <c r="H100" s="16">
         <v>76.058013750000001</v>
       </c>
-      <c r="I100" s="18">
+      <c r="I100" s="16">
         <v>16.383749689999998</v>
       </c>
-      <c r="J100" s="11"/>
-      <c r="K100" s="19">
+      <c r="J100" s="9"/>
+      <c r="K100" s="17">
         <v>77.781546800000001</v>
       </c>
-      <c r="L100" s="19">
+      <c r="L100" s="17">
         <v>23.447214469999999</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A101" s="11"/>
-      <c r="B101" s="16">
+      <c r="A101" s="9"/>
+      <c r="B101" s="14">
         <v>73.396154929999994</v>
       </c>
-      <c r="C101" s="16">
+      <c r="C101" s="14">
         <v>22.81624794</v>
       </c>
-      <c r="D101" s="11"/>
-      <c r="E101" s="17">
+      <c r="D101" s="9"/>
+      <c r="E101" s="15">
         <v>56.666699999999999</v>
       </c>
-      <c r="F101" s="17">
+      <c r="F101" s="15">
         <v>40.640999999999998</v>
       </c>
-      <c r="G101" s="11"/>
-      <c r="H101" s="18">
+      <c r="G101" s="9"/>
+      <c r="H101" s="16">
         <v>57.614674389999998</v>
       </c>
-      <c r="I101" s="18">
+      <c r="I101" s="16">
         <v>33.822447650000001</v>
       </c>
-      <c r="J101" s="11"/>
-      <c r="K101" s="19">
+      <c r="J101" s="9"/>
+      <c r="K101" s="17">
         <v>48.53062937</v>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="17">
         <v>34.152450010000003</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A102" s="11"/>
-      <c r="B102" s="16">
+      <c r="A102" s="9"/>
+      <c r="B102" s="14">
         <v>73.507447729999996</v>
       </c>
-      <c r="C102" s="16">
+      <c r="C102" s="14">
         <v>22.85698876</v>
       </c>
-      <c r="D102" s="11"/>
-      <c r="E102" s="17">
+      <c r="D102" s="9"/>
+      <c r="E102" s="15">
         <v>59.230800000000002</v>
       </c>
-      <c r="F102" s="17">
+      <c r="F102" s="15">
         <v>38.333300000000001</v>
       </c>
-      <c r="G102" s="11"/>
-      <c r="H102" s="18">
+      <c r="G102" s="9"/>
+      <c r="H102" s="16">
         <v>56.17139753</v>
       </c>
-      <c r="I102" s="18">
+      <c r="I102" s="16">
         <v>32.117988769999997</v>
       </c>
-      <c r="J102" s="11"/>
-      <c r="K102" s="19">
+      <c r="J102" s="9"/>
+      <c r="K102" s="17">
         <v>65.530781469999994</v>
       </c>
-      <c r="L102" s="19">
+      <c r="L102" s="17">
         <v>42.281084700000001</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A103" s="11"/>
-      <c r="B103" s="16">
+      <c r="A103" s="9"/>
+      <c r="B103" s="14">
         <v>63.356488110000001</v>
       </c>
-      <c r="C103" s="16">
+      <c r="C103" s="14">
         <v>17.724068840000001</v>
       </c>
-      <c r="D103" s="11"/>
-      <c r="E103" s="17">
+      <c r="D103" s="9"/>
+      <c r="E103" s="15">
         <v>60.769199999999998</v>
       </c>
-      <c r="F103" s="17">
+      <c r="F103" s="15">
         <v>33.718000000000004</v>
       </c>
-      <c r="G103" s="11"/>
-      <c r="H103" s="18">
+      <c r="G103" s="9"/>
+      <c r="H103" s="16">
         <v>66.287890599999997</v>
       </c>
-      <c r="I103" s="18">
+      <c r="I103" s="16">
         <v>26.117109750000001</v>
       </c>
-      <c r="J103" s="11"/>
-      <c r="K103" s="19">
+      <c r="J103" s="9"/>
+      <c r="K103" s="17">
         <v>70.118034140000006</v>
       </c>
-      <c r="L103" s="19">
+      <c r="L103" s="17">
         <v>36.448184789999999</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A104" s="11"/>
-      <c r="B104" s="16">
+      <c r="A104" s="9"/>
+      <c r="B104" s="14">
         <v>72.959046869999995</v>
       </c>
-      <c r="C104" s="16">
+      <c r="C104" s="14">
         <v>22.511499830000002</v>
       </c>
-      <c r="D104" s="11"/>
-      <c r="E104" s="17">
+      <c r="D104" s="9"/>
+      <c r="E104" s="15">
         <v>63.076900000000002</v>
       </c>
-      <c r="F104" s="17">
+      <c r="F104" s="15">
         <v>29.102599999999999</v>
       </c>
-      <c r="G104" s="11"/>
-      <c r="H104" s="18">
+      <c r="G104" s="9"/>
+      <c r="H104" s="16">
         <v>67.881719619999998</v>
       </c>
-      <c r="I104" s="18">
+      <c r="I104" s="16">
         <v>24.23601841</v>
       </c>
-      <c r="J104" s="11"/>
-      <c r="K104" s="19">
+      <c r="J104" s="9"/>
+      <c r="K104" s="17">
         <v>70.472262610000001</v>
       </c>
-      <c r="L104" s="19">
+      <c r="L104" s="17">
         <v>36.08805306</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A105" s="11"/>
-      <c r="B105" s="16">
+      <c r="A105" s="9"/>
+      <c r="B105" s="14">
         <v>64.020841649999994</v>
       </c>
-      <c r="C105" s="16">
+      <c r="C105" s="14">
         <v>17.883581249999999</v>
       </c>
-      <c r="D105" s="11"/>
-      <c r="E105" s="17">
+      <c r="D105" s="9"/>
+      <c r="E105" s="15">
         <v>64.102599999999995</v>
       </c>
-      <c r="F105" s="17">
+      <c r="F105" s="15">
         <v>25.256399999999999</v>
       </c>
-      <c r="G105" s="11"/>
-      <c r="H105" s="18">
+      <c r="G105" s="9"/>
+      <c r="H105" s="16">
         <v>64.028081299999997</v>
       </c>
-      <c r="I105" s="18">
+      <c r="I105" s="16">
         <v>27.672685510000001</v>
       </c>
-      <c r="J105" s="11"/>
-      <c r="K105" s="19">
+      <c r="J105" s="9"/>
+      <c r="K105" s="17">
         <v>76.791130069999994</v>
       </c>
-      <c r="L105" s="19">
+      <c r="L105" s="17">
         <v>28.07200817</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A106" s="11"/>
-      <c r="B106" s="16">
+      <c r="A106" s="9"/>
+      <c r="B106" s="14">
         <v>61.124463239999997</v>
       </c>
-      <c r="C106" s="16">
+      <c r="C106" s="14">
         <v>17.116353360000002</v>
       </c>
-      <c r="D106" s="11"/>
-      <c r="E106" s="17">
+      <c r="D106" s="9"/>
+      <c r="E106" s="15">
         <v>64.358999999999995</v>
       </c>
-      <c r="F106" s="17">
+      <c r="F106" s="15">
         <v>24.102599999999999</v>
       </c>
-      <c r="G106" s="11"/>
-      <c r="H106" s="18">
+      <c r="G106" s="9"/>
+      <c r="H106" s="16">
         <v>77.496651749999998</v>
       </c>
-      <c r="I106" s="18">
+      <c r="I106" s="16">
         <v>14.94852356</v>
       </c>
-      <c r="J106" s="11"/>
-      <c r="K106" s="19">
+      <c r="J106" s="9"/>
+      <c r="K106" s="17">
         <v>72.409354590000007</v>
       </c>
-      <c r="L106" s="19">
+      <c r="L106" s="17">
         <v>33.039256969999997</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A107" s="11"/>
-      <c r="B107" s="16">
+      <c r="A107" s="9"/>
+      <c r="B107" s="14">
         <v>75.674207330000002</v>
       </c>
-      <c r="C107" s="16">
+      <c r="C107" s="14">
         <v>24.782500970000001</v>
       </c>
-      <c r="D107" s="11"/>
-      <c r="E107" s="17">
+      <c r="D107" s="9"/>
+      <c r="E107" s="15">
         <v>74.358999999999995</v>
       </c>
-      <c r="F107" s="17">
+      <c r="F107" s="15">
         <v>22.948699999999999</v>
       </c>
-      <c r="G107" s="11"/>
-      <c r="H107" s="18">
+      <c r="G107" s="9"/>
+      <c r="H107" s="16">
         <v>77.634651759999997</v>
       </c>
-      <c r="I107" s="18">
+      <c r="I107" s="16">
         <v>14.46185393</v>
       </c>
-      <c r="J107" s="11"/>
-      <c r="K107" s="19">
+      <c r="J107" s="9"/>
+      <c r="K107" s="17">
         <v>76.271299819999996</v>
       </c>
-      <c r="L107" s="19">
+      <c r="L107" s="17">
         <v>25.569544149999999</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A108" s="11"/>
-      <c r="B108" s="16">
+      <c r="A108" s="9"/>
+      <c r="B108" s="14">
         <v>69.513583159999996</v>
       </c>
-      <c r="C108" s="16">
+      <c r="C108" s="14">
         <v>20.27935789</v>
       </c>
-      <c r="D108" s="11"/>
-      <c r="E108" s="17">
+      <c r="D108" s="9"/>
+      <c r="E108" s="15">
         <v>71.2821</v>
       </c>
-      <c r="F108" s="17">
+      <c r="F108" s="15">
         <v>22.948699999999999</v>
       </c>
-      <c r="G108" s="11"/>
-      <c r="H108" s="18">
+      <c r="G108" s="9"/>
+      <c r="H108" s="16">
         <v>77.86372643</v>
       </c>
-      <c r="I108" s="18">
+      <c r="I108" s="16">
         <v>14.61067765</v>
       </c>
-      <c r="J108" s="11"/>
-      <c r="K108" s="19">
+      <c r="J108" s="9"/>
+      <c r="K108" s="17">
         <v>76.95325914</v>
       </c>
-      <c r="L108" s="19">
+      <c r="L108" s="17">
         <v>27.770610739999999</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A109" s="11"/>
-      <c r="B109" s="16">
+      <c r="A109" s="9"/>
+      <c r="B109" s="14">
         <v>58.572135469999999</v>
       </c>
-      <c r="C109" s="16">
+      <c r="C109" s="14">
         <v>16.64270381</v>
       </c>
-      <c r="D109" s="11"/>
-      <c r="E109" s="17">
+      <c r="D109" s="9"/>
+      <c r="E109" s="15">
         <v>67.948700000000002</v>
       </c>
-      <c r="F109" s="17">
+      <c r="F109" s="15">
         <v>22.179500000000001</v>
       </c>
-      <c r="G109" s="11"/>
-      <c r="H109" s="18">
+      <c r="G109" s="9"/>
+      <c r="H109" s="16">
         <v>77.33815817</v>
       </c>
-      <c r="I109" s="18">
+      <c r="I109" s="16">
         <v>15.890054660000001</v>
       </c>
-      <c r="J109" s="11"/>
-      <c r="K109" s="19">
+      <c r="J109" s="9"/>
+      <c r="K109" s="17">
         <v>75.107730090000004</v>
       </c>
-      <c r="L109" s="19">
+      <c r="L109" s="17">
         <v>30.016983419999999</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" s="11"/>
-      <c r="B110" s="16">
+      <c r="A110" s="9"/>
+      <c r="B110" s="14">
         <v>70.981940989999998</v>
       </c>
-      <c r="C110" s="16">
+      <c r="C110" s="14">
         <v>21.145888100000001</v>
       </c>
-      <c r="D110" s="11"/>
-      <c r="E110" s="17">
+      <c r="D110" s="9"/>
+      <c r="E110" s="15">
         <v>65.897400000000005</v>
       </c>
-      <c r="F110" s="17">
+      <c r="F110" s="15">
         <v>20.256399999999999</v>
       </c>
-      <c r="G110" s="11"/>
-      <c r="H110" s="18">
+      <c r="G110" s="9"/>
+      <c r="H110" s="16">
         <v>76.180416530000002</v>
       </c>
-      <c r="I110" s="18">
+      <c r="I110" s="16">
         <v>15.91257375</v>
       </c>
-      <c r="J110" s="11"/>
-      <c r="K110" s="19">
+      <c r="J110" s="9"/>
+      <c r="K110" s="17">
         <v>75.969285200000002</v>
       </c>
-      <c r="L110" s="19">
+      <c r="L110" s="17">
         <v>29.038865380000001</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A111" s="11"/>
-      <c r="B111" s="16">
+      <c r="A111" s="9"/>
+      <c r="B111" s="14">
         <v>65.223030399999999</v>
       </c>
-      <c r="C111" s="16">
+      <c r="C111" s="14">
         <v>18.397195119999999</v>
       </c>
-      <c r="D111" s="11"/>
-      <c r="E111" s="17">
+      <c r="D111" s="9"/>
+      <c r="E111" s="15">
         <v>63.076900000000002</v>
       </c>
-      <c r="F111" s="17">
+      <c r="F111" s="15">
         <v>19.102599999999999</v>
       </c>
-      <c r="G111" s="11"/>
-      <c r="H111" s="18">
+      <c r="G111" s="9"/>
+      <c r="H111" s="16">
         <v>77.252651090000001</v>
       </c>
-      <c r="I111" s="18">
+      <c r="I111" s="16">
         <v>15.15151702</v>
       </c>
-      <c r="J111" s="11"/>
-      <c r="K111" s="19">
+      <c r="J111" s="9"/>
+      <c r="K111" s="17">
         <v>75.283887010000001</v>
       </c>
-      <c r="L111" s="19">
+      <c r="L111" s="17">
         <v>24.874753170000002</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="11"/>
-      <c r="B112" s="16">
+      <c r="A112" s="9"/>
+      <c r="B112" s="14">
         <v>65.31504391</v>
       </c>
-      <c r="C112" s="16">
+      <c r="C112" s="14">
         <v>18.3337483</v>
       </c>
-      <c r="D112" s="11"/>
-      <c r="E112" s="17">
+      <c r="D112" s="9"/>
+      <c r="E112" s="15">
         <v>61.2821</v>
       </c>
-      <c r="F112" s="17">
+      <c r="F112" s="15">
         <v>19.102599999999999</v>
       </c>
-      <c r="G112" s="11"/>
-      <c r="H112" s="18">
+      <c r="G112" s="9"/>
+      <c r="H112" s="16">
         <v>77.413375279999997</v>
       </c>
-      <c r="I112" s="18">
+      <c r="I112" s="16">
         <v>15.22192798</v>
       </c>
-      <c r="J112" s="11"/>
-      <c r="K112" s="19">
+      <c r="J112" s="9"/>
+      <c r="K112" s="17">
         <v>77.052240639999994</v>
       </c>
-      <c r="L112" s="19">
+      <c r="L112" s="17">
         <v>27.905639090000001</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A113" s="11"/>
-      <c r="B113" s="16">
+      <c r="A113" s="9"/>
+      <c r="B113" s="14">
         <v>64.010240679999995</v>
       </c>
-      <c r="C113" s="16">
+      <c r="C113" s="14">
         <v>17.924478189999999</v>
       </c>
-      <c r="D113" s="11"/>
-      <c r="E113" s="17">
+      <c r="D113" s="9"/>
+      <c r="E113" s="15">
         <v>58.7179</v>
       </c>
-      <c r="F113" s="17">
+      <c r="F113" s="15">
         <v>18.333300000000001</v>
       </c>
-      <c r="G113" s="11"/>
-      <c r="H113" s="18">
+      <c r="G113" s="9"/>
+      <c r="H113" s="16">
         <v>76.731849400000002</v>
       </c>
-      <c r="I113" s="18">
+      <c r="I113" s="16">
         <v>16.216846140000001</v>
       </c>
-      <c r="J113" s="11"/>
-      <c r="K113" s="19">
+      <c r="J113" s="9"/>
+      <c r="K113" s="17">
         <v>42.826756340000003</v>
       </c>
-      <c r="L113" s="19">
+      <c r="L113" s="17">
         <v>25.556959410000001</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A114" s="11"/>
-      <c r="B114" s="16">
+      <c r="A114" s="9"/>
+      <c r="B114" s="14">
         <v>57.140935929999998</v>
       </c>
-      <c r="C114" s="16">
+      <c r="C114" s="14">
         <v>16.598610539999999</v>
       </c>
-      <c r="D114" s="11"/>
-      <c r="E114" s="17">
+      <c r="D114" s="9"/>
+      <c r="E114" s="15">
         <v>55.1282</v>
       </c>
-      <c r="F114" s="17">
+      <c r="F114" s="15">
         <v>18.333300000000001</v>
       </c>
-      <c r="G114" s="11"/>
-      <c r="H114" s="18">
+      <c r="G114" s="9"/>
+      <c r="H114" s="16">
         <v>49.47110541</v>
       </c>
-      <c r="I114" s="18">
+      <c r="I114" s="16">
         <v>25.063019310000001</v>
       </c>
-      <c r="J114" s="11"/>
-      <c r="K114" s="19">
+      <c r="J114" s="9"/>
+      <c r="K114" s="17">
         <v>42.080660690000002</v>
       </c>
-      <c r="L114" s="19">
+      <c r="L114" s="17">
         <v>24.94652645</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A115" s="11"/>
-      <c r="B115" s="16">
+      <c r="A115" s="9"/>
+      <c r="B115" s="14">
         <v>56.36515326</v>
       </c>
-      <c r="C115" s="16">
+      <c r="C115" s="14">
         <v>16.326546369999999</v>
       </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="17">
+      <c r="D115" s="9"/>
+      <c r="E115" s="15">
         <v>52.307699999999997</v>
       </c>
-      <c r="F115" s="17">
+      <c r="F115" s="15">
         <v>18.333300000000001</v>
       </c>
-      <c r="G115" s="11"/>
-      <c r="H115" s="18">
+      <c r="G115" s="9"/>
+      <c r="H115" s="16">
         <v>42.476539940000002</v>
       </c>
-      <c r="I115" s="18">
+      <c r="I115" s="16">
         <v>18.338473560000001</v>
       </c>
-      <c r="J115" s="11"/>
-      <c r="K115" s="19">
+      <c r="J115" s="9"/>
+      <c r="K115" s="17">
         <v>39.878304649999997</v>
       </c>
-      <c r="L115" s="19">
+      <c r="L115" s="17">
         <v>18.324929220000001</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A116" s="11"/>
-      <c r="B116" s="16">
+      <c r="A116" s="9"/>
+      <c r="B116" s="14">
         <v>43.046183239999998</v>
       </c>
-      <c r="C116" s="16">
+      <c r="C116" s="14">
         <v>18.40255939</v>
       </c>
-      <c r="D116" s="11"/>
-      <c r="E116" s="17">
+      <c r="D116" s="9"/>
+      <c r="E116" s="15">
         <v>49.743600000000001</v>
       </c>
-      <c r="F116" s="17">
+      <c r="F116" s="15">
         <v>17.5641</v>
       </c>
-      <c r="G116" s="11"/>
-      <c r="H116" s="18">
+      <c r="G116" s="9"/>
+      <c r="H116" s="16">
         <v>43.59511586</v>
       </c>
-      <c r="I116" s="18">
+      <c r="I116" s="16">
         <v>19.994200979999999</v>
       </c>
-      <c r="J116" s="11"/>
-      <c r="K116" s="19">
+      <c r="J116" s="9"/>
+      <c r="K116" s="17">
         <v>36.475499169999999</v>
       </c>
-      <c r="L116" s="19">
+      <c r="L116" s="17">
         <v>17.718947790000001</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A117" s="11"/>
-      <c r="B117" s="16">
+      <c r="A117" s="9"/>
+      <c r="B117" s="14">
         <v>52.081755559999998</v>
       </c>
-      <c r="C117" s="16">
+      <c r="C117" s="14">
         <v>16.45387453</v>
       </c>
-      <c r="D117" s="11"/>
-      <c r="E117" s="17">
+      <c r="D117" s="9"/>
+      <c r="E117" s="15">
         <v>47.435899999999997</v>
       </c>
-      <c r="F117" s="17">
+      <c r="F117" s="15">
         <v>16.025600000000001</v>
       </c>
-      <c r="G117" s="11"/>
-      <c r="H117" s="18">
+      <c r="G117" s="9"/>
+      <c r="H117" s="16">
         <v>50.339969670000002</v>
       </c>
-      <c r="I117" s="18">
+      <c r="I117" s="16">
         <v>26.471396609999999</v>
       </c>
-      <c r="J117" s="11"/>
-      <c r="K117" s="19">
+      <c r="J117" s="9"/>
+      <c r="K117" s="17">
         <v>37.103073639999998</v>
       </c>
-      <c r="L117" s="19">
+      <c r="L117" s="17">
         <v>15.44561165</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A118" s="11"/>
-      <c r="B118" s="16">
+      <c r="A118" s="9"/>
+      <c r="B118" s="14">
         <v>42.87903652</v>
       </c>
-      <c r="C118" s="16">
+      <c r="C118" s="14">
         <v>18.489411029999999</v>
       </c>
-      <c r="D118" s="11"/>
-      <c r="E118" s="17">
+      <c r="D118" s="9"/>
+      <c r="E118" s="15">
         <v>44.8718</v>
       </c>
-      <c r="F118" s="17">
+      <c r="F118" s="15">
         <v>13.718</v>
       </c>
-      <c r="G118" s="11"/>
-      <c r="H118" s="18">
+      <c r="G118" s="9"/>
+      <c r="H118" s="16">
         <v>40.748980260000003</v>
       </c>
-      <c r="I118" s="18">
+      <c r="I118" s="16">
         <v>16.182141659999999</v>
       </c>
-      <c r="J118" s="11"/>
-      <c r="K118" s="19">
+      <c r="J118" s="9"/>
+      <c r="K118" s="17">
         <v>34.14896821</v>
       </c>
-      <c r="L118" s="19">
+      <c r="L118" s="17">
         <v>13.52386987</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A119" s="11"/>
-      <c r="B119" s="16">
+      <c r="A119" s="9"/>
+      <c r="B119" s="14">
         <v>51.566994800000003</v>
       </c>
-      <c r="C119" s="16">
+      <c r="C119" s="14">
         <v>16.48571364</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="17">
+      <c r="D119" s="9"/>
+      <c r="E119" s="15">
         <v>48.7179</v>
       </c>
-      <c r="F119" s="17">
+      <c r="F119" s="15">
         <v>14.8718</v>
       </c>
-      <c r="G119" s="11"/>
-      <c r="H119" s="18">
+      <c r="G119" s="9"/>
+      <c r="H119" s="16">
         <v>38.386525579999997</v>
       </c>
-      <c r="I119" s="18">
+      <c r="I119" s="16">
         <v>14.580215150000001</v>
       </c>
-      <c r="J119" s="11"/>
-      <c r="K119" s="19">
+      <c r="J119" s="9"/>
+      <c r="K119" s="17">
         <v>37.579421910000001</v>
       </c>
-      <c r="L119" s="19">
+      <c r="L119" s="17">
         <v>15.015890130000001</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A120" s="11"/>
-      <c r="B120" s="16">
+      <c r="A120" s="9"/>
+      <c r="B120" s="14">
         <v>58.839125119999999</v>
       </c>
-      <c r="C120" s="16">
+      <c r="C120" s="14">
         <v>16.63763522</v>
       </c>
-      <c r="D120" s="11"/>
-      <c r="E120" s="17">
+      <c r="D120" s="9"/>
+      <c r="E120" s="15">
         <v>51.2821</v>
       </c>
-      <c r="F120" s="17">
+      <c r="F120" s="15">
         <v>14.8718</v>
       </c>
-      <c r="G120" s="11"/>
-      <c r="H120" s="18">
+      <c r="G120" s="9"/>
+      <c r="H120" s="16">
         <v>38.404015209999997</v>
       </c>
-      <c r="I120" s="18">
+      <c r="I120" s="16">
         <v>14.45194845</v>
       </c>
-      <c r="J120" s="11"/>
-      <c r="K120" s="19">
+      <c r="J120" s="9"/>
+      <c r="K120" s="17">
         <v>41.064305789999999</v>
       </c>
-      <c r="L120" s="19">
+      <c r="L120" s="17">
         <v>12.214468930000001</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A121" s="11"/>
-      <c r="B121" s="16">
+      <c r="A121" s="9"/>
+      <c r="B121" s="14">
         <v>60.755789139999997</v>
       </c>
-      <c r="C121" s="16">
+      <c r="C121" s="14">
         <v>17.03323151</v>
       </c>
-      <c r="D121" s="11"/>
-      <c r="E121" s="17">
+      <c r="D121" s="9"/>
+      <c r="E121" s="15">
         <v>54.102600000000002</v>
       </c>
-      <c r="F121" s="17">
+      <c r="F121" s="15">
         <v>14.8718</v>
       </c>
-      <c r="G121" s="11"/>
-      <c r="H121" s="18">
+      <c r="G121" s="9"/>
+      <c r="H121" s="16">
         <v>38.76427889</v>
       </c>
-      <c r="I121" s="18">
+      <c r="I121" s="16">
         <v>14.365590470000001</v>
       </c>
-      <c r="J121" s="11"/>
-      <c r="K121" s="19">
+      <c r="J121" s="9"/>
+      <c r="K121" s="17">
         <v>42.195266150000002</v>
       </c>
-      <c r="L121" s="19">
+      <c r="L121" s="17">
         <v>20.919372190000001</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A122" s="11"/>
-      <c r="B122" s="16">
+      <c r="A122" s="9"/>
+      <c r="B122" s="14">
         <v>54.761156120000003</v>
       </c>
-      <c r="C122" s="16">
+      <c r="C122" s="14">
         <v>16.3661891</v>
       </c>
-      <c r="D122" s="11"/>
-      <c r="E122" s="17">
+      <c r="D122" s="9"/>
+      <c r="E122" s="15">
         <v>56.153799999999997</v>
       </c>
-      <c r="F122" s="17">
+      <c r="F122" s="15">
         <v>14.102600000000001</v>
       </c>
-      <c r="G122" s="11"/>
-      <c r="H122" s="18">
+      <c r="G122" s="9"/>
+      <c r="H122" s="16">
         <v>41.470142330000002</v>
       </c>
-      <c r="I122" s="18">
+      <c r="I122" s="16">
         <v>17.278033440000002</v>
       </c>
-      <c r="J122" s="11"/>
-      <c r="K122" s="19">
+      <c r="J122" s="9"/>
+      <c r="K122" s="17">
         <v>36.60557824</v>
       </c>
-      <c r="L122" s="19">
+      <c r="L122" s="17">
         <v>15.748875890000001</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A123" s="11"/>
-      <c r="B123" s="16">
+      <c r="A123" s="9"/>
+      <c r="B123" s="14">
         <v>53.569904999999999</v>
       </c>
-      <c r="C123" s="16">
+      <c r="C123" s="14">
         <v>16.339712550000002</v>
       </c>
-      <c r="D123" s="11"/>
-      <c r="E123" s="17">
+      <c r="D123" s="9"/>
+      <c r="E123" s="15">
         <v>52.051299999999998</v>
       </c>
-      <c r="F123" s="17">
+      <c r="F123" s="15">
         <v>12.5641</v>
       </c>
-      <c r="G123" s="11"/>
-      <c r="H123" s="18">
+      <c r="G123" s="9"/>
+      <c r="H123" s="16">
         <v>47.15540481</v>
       </c>
-      <c r="I123" s="18">
+      <c r="I123" s="16">
         <v>22.377932529999999</v>
       </c>
-      <c r="J123" s="11"/>
-      <c r="K123" s="19">
+      <c r="J123" s="9"/>
+      <c r="K123" s="17">
         <v>39.431161209999999</v>
       </c>
-      <c r="L123" s="19">
+      <c r="L123" s="17">
         <v>19.323840749999999</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A124" s="11"/>
-      <c r="B124" s="16">
+      <c r="A124" s="9"/>
+      <c r="B124" s="14">
         <v>48.914618240000003</v>
       </c>
-      <c r="C124" s="16">
+      <c r="C124" s="14">
         <v>16.798637079999999</v>
       </c>
-      <c r="D124" s="11"/>
-      <c r="E124" s="17">
+      <c r="D124" s="9"/>
+      <c r="E124" s="15">
         <v>48.7179</v>
       </c>
-      <c r="F124" s="17">
+      <c r="F124" s="15">
         <v>11.025600000000001</v>
       </c>
-      <c r="G124" s="11"/>
-      <c r="H124" s="18">
+      <c r="G124" s="9"/>
+      <c r="H124" s="16">
         <v>39.582566749999998</v>
       </c>
-      <c r="I124" s="18">
+      <c r="I124" s="16">
         <v>17.648452840000001</v>
       </c>
-      <c r="J124" s="11"/>
-      <c r="K124" s="19">
+      <c r="J124" s="9"/>
+      <c r="K124" s="17">
         <v>37.562076339999997</v>
       </c>
-      <c r="L124" s="19">
+      <c r="L124" s="17">
         <v>11.928445699999999</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A125" s="11"/>
-      <c r="B125" s="16">
+      <c r="A125" s="9"/>
+      <c r="B125" s="14">
         <v>52.64613731</v>
       </c>
-      <c r="C125" s="16">
+      <c r="C125" s="14">
         <v>16.384836379999999</v>
       </c>
-      <c r="D125" s="11"/>
-      <c r="E125" s="17">
+      <c r="D125" s="9"/>
+      <c r="E125" s="15">
         <v>47.179499999999997</v>
       </c>
-      <c r="F125" s="17">
+      <c r="F125" s="15">
         <v>9.8718000000000004</v>
       </c>
-      <c r="G125" s="11"/>
-      <c r="H125" s="18">
+      <c r="G125" s="9"/>
+      <c r="H125" s="16">
         <v>41.740243820000003</v>
       </c>
-      <c r="I125" s="18">
+      <c r="I125" s="16">
         <v>17.829324310000001</v>
       </c>
-      <c r="J125" s="11"/>
-      <c r="K125" s="19">
+      <c r="J125" s="9"/>
+      <c r="K125" s="17">
         <v>34.238110040000002</v>
       </c>
-      <c r="L125" s="19">
+      <c r="L125" s="17">
         <v>13.713158229999999</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A126" s="11"/>
-      <c r="B126" s="16">
+      <c r="A126" s="9"/>
+      <c r="B126" s="14">
         <v>49.838492989999999</v>
       </c>
-      <c r="C126" s="16">
+      <c r="C126" s="14">
         <v>16.676330279999998</v>
       </c>
-      <c r="D126" s="11"/>
-      <c r="E126" s="17">
+      <c r="D126" s="9"/>
+      <c r="E126" s="15">
         <v>46.153799999999997</v>
       </c>
-      <c r="F126" s="17">
+      <c r="F126" s="15">
         <v>6.0255999999999998</v>
       </c>
-      <c r="G126" s="11"/>
-      <c r="H126" s="18">
+      <c r="G126" s="9"/>
+      <c r="H126" s="16">
         <v>39.311871889999999</v>
       </c>
-      <c r="I126" s="18">
+      <c r="I126" s="16">
         <v>15.64071697</v>
       </c>
-      <c r="J126" s="11"/>
-      <c r="K126" s="19">
+      <c r="J126" s="9"/>
+      <c r="K126" s="17">
         <v>34.140941040000001</v>
       </c>
-      <c r="L126" s="19">
+      <c r="L126" s="17">
         <v>4.5776613499999996</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A127" s="11"/>
-      <c r="B127" s="16">
+      <c r="A127" s="9"/>
+      <c r="B127" s="14">
         <v>52.684066399999999</v>
       </c>
-      <c r="C127" s="16">
+      <c r="C127" s="14">
         <v>16.407962779999998</v>
       </c>
-      <c r="D127" s="11"/>
-      <c r="E127" s="17">
+      <c r="D127" s="9"/>
+      <c r="E127" s="15">
         <v>50.512799999999999</v>
       </c>
-      <c r="F127" s="17">
+      <c r="F127" s="15">
         <v>9.4871999999999996</v>
       </c>
-      <c r="G127" s="11"/>
-      <c r="H127" s="18">
+      <c r="G127" s="9"/>
+      <c r="H127" s="16">
         <v>41.679847690000003</v>
       </c>
-      <c r="I127" s="18">
+      <c r="I127" s="16">
         <v>17.745919010000001</v>
       </c>
-      <c r="J127" s="11"/>
-      <c r="K127" s="19">
+      <c r="J127" s="9"/>
+      <c r="K127" s="17">
         <v>36.659267700000001</v>
       </c>
-      <c r="L127" s="19">
+      <c r="L127" s="17">
         <v>17.68196446</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A128" s="11"/>
-      <c r="B128" s="16">
+      <c r="A128" s="9"/>
+      <c r="B128" s="14">
         <v>65.807219029999999</v>
       </c>
-      <c r="C128" s="16">
+      <c r="C128" s="14">
         <v>18.140764950000001</v>
       </c>
-      <c r="D128" s="11"/>
-      <c r="E128" s="17">
+      <c r="D128" s="9"/>
+      <c r="E128" s="15">
         <v>53.846200000000003</v>
       </c>
-      <c r="F128" s="17">
+      <c r="F128" s="15">
         <v>10.256399999999999</v>
       </c>
-      <c r="G128" s="11"/>
-      <c r="H128" s="18">
+      <c r="G128" s="9"/>
+      <c r="H128" s="16">
         <v>39.087464449999999</v>
       </c>
-      <c r="I128" s="18">
+      <c r="I128" s="16">
         <v>15.12230394</v>
       </c>
-      <c r="J128" s="11"/>
-      <c r="K128" s="19">
+      <c r="J128" s="9"/>
+      <c r="K128" s="17">
         <v>40.643719279999999</v>
       </c>
-      <c r="L128" s="19">
+      <c r="L128" s="17">
         <v>20.240861370000001</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A129" s="11"/>
-      <c r="B129" s="16">
+      <c r="A129" s="9"/>
+      <c r="B129" s="14">
         <v>60.67392092</v>
       </c>
-      <c r="C129" s="16">
+      <c r="C129" s="14">
         <v>17.05180236</v>
       </c>
-      <c r="D129" s="11"/>
-      <c r="E129" s="17">
+      <c r="D129" s="9"/>
+      <c r="E129" s="15">
         <v>57.435899999999997</v>
       </c>
-      <c r="F129" s="17">
+      <c r="F129" s="15">
         <v>10.256399999999999</v>
       </c>
-      <c r="G129" s="11"/>
-      <c r="H129" s="18">
+      <c r="G129" s="9"/>
+      <c r="H129" s="16">
         <v>41.481502859999999</v>
       </c>
-      <c r="I129" s="18">
+      <c r="I129" s="16">
         <v>18.047437439999999</v>
       </c>
-      <c r="J129" s="11"/>
-      <c r="K129" s="19">
+      <c r="J129" s="9"/>
+      <c r="K129" s="17">
         <v>36.792481590000001</v>
       </c>
-      <c r="L129" s="19">
+      <c r="L129" s="17">
         <v>13.39213473</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A130" s="11"/>
-      <c r="B130" s="16">
+      <c r="A130" s="9"/>
+      <c r="B130" s="14">
         <v>63.394712869999999</v>
       </c>
-      <c r="C130" s="16">
+      <c r="C130" s="14">
         <v>17.70053514</v>
       </c>
-      <c r="D130" s="11"/>
-      <c r="E130" s="17">
+      <c r="D130" s="9"/>
+      <c r="E130" s="15">
         <v>60</v>
       </c>
-      <c r="F130" s="17">
+      <c r="F130" s="15">
         <v>10.641</v>
       </c>
-      <c r="G130" s="11"/>
-      <c r="H130" s="18">
+      <c r="G130" s="9"/>
+      <c r="H130" s="16">
         <v>77.606086550000001</v>
       </c>
-      <c r="I130" s="18">
+      <c r="I130" s="16">
         <v>15.16287254</v>
       </c>
-      <c r="J130" s="11"/>
-      <c r="K130" s="19">
+      <c r="J130" s="9"/>
+      <c r="K130" s="17">
         <v>75.948300639999999</v>
       </c>
-      <c r="L130" s="19">
+      <c r="L130" s="17">
         <v>22.744795910000001</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A131" s="11"/>
-      <c r="B131" s="16">
+      <c r="A131" s="9"/>
+      <c r="B131" s="14">
         <v>64.80200945</v>
       </c>
-      <c r="C131" s="16">
+      <c r="C131" s="14">
         <v>18.21687863</v>
       </c>
-      <c r="D131" s="11"/>
-      <c r="E131" s="17">
+      <c r="D131" s="9"/>
+      <c r="E131" s="15">
         <v>64.102599999999995</v>
       </c>
-      <c r="F131" s="17">
+      <c r="F131" s="15">
         <v>10.641</v>
       </c>
-      <c r="G131" s="11"/>
-      <c r="H131" s="18">
+      <c r="G131" s="9"/>
+      <c r="H131" s="16">
         <v>75.982661519999994</v>
       </c>
-      <c r="I131" s="18">
+      <c r="I131" s="16">
         <v>16.30692238</v>
       </c>
-      <c r="J131" s="11"/>
-      <c r="K131" s="19">
+      <c r="J131" s="9"/>
+      <c r="K131" s="17">
         <v>76.840692469999993</v>
       </c>
-      <c r="L131" s="19">
+      <c r="L131" s="17">
         <v>20.918547220000001</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A132" s="11"/>
-      <c r="B132" s="16">
+      <c r="A132" s="9"/>
+      <c r="B132" s="14">
         <v>65.025939809999997</v>
       </c>
-      <c r="C132" s="16">
+      <c r="C132" s="14">
         <v>18.287824499999999</v>
       </c>
-      <c r="D132" s="11"/>
-      <c r="E132" s="17">
+      <c r="D132" s="9"/>
+      <c r="E132" s="15">
         <v>66.923100000000005</v>
       </c>
-      <c r="F132" s="17">
+      <c r="F132" s="15">
         <v>10.641</v>
       </c>
-      <c r="G132" s="11"/>
-      <c r="H132" s="18">
+      <c r="G132" s="9"/>
+      <c r="H132" s="16">
         <v>76.945757240000006</v>
       </c>
-      <c r="I132" s="18">
+      <c r="I132" s="16">
         <v>15.858478330000001</v>
       </c>
-      <c r="J132" s="11"/>
-      <c r="K132" s="19">
+      <c r="J132" s="9"/>
+      <c r="K132" s="17">
         <v>81.950477640000003</v>
       </c>
-      <c r="L132" s="19">
+      <c r="L132" s="17">
         <v>19.87455821</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A133" s="11"/>
-      <c r="B133" s="16">
+      <c r="A133" s="9"/>
+      <c r="B133" s="14">
         <v>65.755551539999999</v>
       </c>
-      <c r="C133" s="16">
+      <c r="C133" s="14">
         <v>18.51621583</v>
       </c>
-      <c r="D133" s="11"/>
-      <c r="E133" s="17">
+      <c r="D133" s="9"/>
+      <c r="E133" s="15">
         <v>71.2821</v>
       </c>
-      <c r="F133" s="17">
+      <c r="F133" s="15">
         <v>10.641</v>
       </c>
-      <c r="G133" s="11"/>
-      <c r="H133" s="18">
+      <c r="G133" s="9"/>
+      <c r="H133" s="16">
         <v>77.543720070000006</v>
       </c>
-      <c r="I133" s="18">
+      <c r="I133" s="16">
         <v>15.25394915</v>
       </c>
-      <c r="J133" s="11"/>
-      <c r="K133" s="19">
+      <c r="J133" s="9"/>
+      <c r="K133" s="17">
         <v>81.643705690000004</v>
       </c>
-      <c r="L133" s="19">
+      <c r="L133" s="17">
         <v>16.591759979999999</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A134" s="11"/>
-      <c r="B134" s="16">
+      <c r="A134" s="9"/>
+      <c r="B134" s="14">
         <v>69.967734120000003</v>
       </c>
-      <c r="C134" s="16">
+      <c r="C134" s="14">
         <v>20.53898878</v>
       </c>
-      <c r="D134" s="11"/>
-      <c r="E134" s="17">
+      <c r="D134" s="9"/>
+      <c r="E134" s="15">
         <v>74.358999999999995</v>
       </c>
-      <c r="F134" s="17">
+      <c r="F134" s="15">
         <v>10.641</v>
       </c>
-      <c r="G134" s="11"/>
-      <c r="H134" s="18">
+      <c r="G134" s="9"/>
+      <c r="H134" s="16">
         <v>77.584739839999997</v>
       </c>
-      <c r="I134" s="18">
+      <c r="I134" s="16">
         <v>15.83003939</v>
       </c>
-      <c r="J134" s="11"/>
-      <c r="K134" s="19">
+      <c r="J134" s="9"/>
+      <c r="K134" s="17">
         <v>84.610219779999994</v>
       </c>
-      <c r="L134" s="19">
+      <c r="L134" s="17">
         <v>14.2477619</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A135" s="11"/>
-      <c r="B135" s="16">
+      <c r="A135" s="9"/>
+      <c r="B135" s="14">
         <v>68.892784019999993</v>
       </c>
-      <c r="C135" s="16">
+      <c r="C135" s="14">
         <v>20.032448840000001</v>
       </c>
-      <c r="D135" s="11"/>
-      <c r="E135" s="17">
+      <c r="D135" s="9"/>
+      <c r="E135" s="15">
         <v>78.205100000000002</v>
       </c>
-      <c r="F135" s="17">
+      <c r="F135" s="15">
         <v>10.641</v>
       </c>
-      <c r="G135" s="11"/>
-      <c r="H135" s="18">
+      <c r="G135" s="9"/>
+      <c r="H135" s="16">
         <v>76.822304259999996</v>
       </c>
-      <c r="I135" s="18">
+      <c r="I135" s="16">
         <v>15.59516532</v>
       </c>
-      <c r="J135" s="11"/>
-      <c r="K135" s="19">
+      <c r="J135" s="9"/>
+      <c r="K135" s="17">
         <v>84.102879430000002</v>
       </c>
-      <c r="L135" s="19">
+      <c r="L135" s="17">
         <v>8.9806557900000001</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A136" s="11"/>
-      <c r="B136" s="16">
+      <c r="A136" s="9"/>
+      <c r="B136" s="14">
         <v>61.826546559999997</v>
       </c>
-      <c r="C136" s="16">
+      <c r="C136" s="14">
         <v>17.269655449999998</v>
       </c>
-      <c r="D136" s="11"/>
-      <c r="E136" s="17">
+      <c r="D136" s="9"/>
+      <c r="E136" s="15">
         <v>67.948700000000002</v>
       </c>
-      <c r="F136" s="17">
+      <c r="F136" s="15">
         <v>8.718</v>
       </c>
-      <c r="G136" s="11"/>
-      <c r="H136" s="18">
+      <c r="G136" s="9"/>
+      <c r="H136" s="16">
         <v>77.348571660000005</v>
       </c>
-      <c r="I136" s="18">
+      <c r="I136" s="16">
         <v>15.77452924</v>
       </c>
-      <c r="J136" s="11"/>
-      <c r="K136" s="19">
+      <c r="J136" s="9"/>
+      <c r="K136" s="17">
         <v>80.180025450000002</v>
       </c>
-      <c r="L136" s="19">
+      <c r="L136" s="17">
         <v>19.088844129999998</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A137" s="11"/>
-      <c r="B137" s="16">
+      <c r="A137" s="9"/>
+      <c r="B137" s="14">
         <v>60.787970080000001</v>
       </c>
-      <c r="C137" s="16">
+      <c r="C137" s="14">
         <v>17.04620486</v>
       </c>
-      <c r="D137" s="11"/>
-      <c r="E137" s="17">
+      <c r="D137" s="9"/>
+      <c r="E137" s="15">
         <v>68.461500000000001</v>
       </c>
-      <c r="F137" s="17">
+      <c r="F137" s="15">
         <v>5.2564000000000002</v>
       </c>
-      <c r="G137" s="11"/>
-      <c r="H137" s="18">
+      <c r="G137" s="9"/>
+      <c r="H137" s="16">
         <v>77.573152690000001</v>
       </c>
-      <c r="I137" s="18">
+      <c r="I137" s="16">
         <v>14.780645829999999</v>
       </c>
-      <c r="J137" s="11"/>
-      <c r="K137" s="19">
+      <c r="J137" s="9"/>
+      <c r="K137" s="17">
         <v>80.573272990000007</v>
       </c>
-      <c r="L137" s="19">
+      <c r="L137" s="17">
         <v>8.3656389020000006</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A138" s="11"/>
-      <c r="B138" s="16">
+      <c r="A138" s="9"/>
+      <c r="B138" s="14">
         <v>61.91560964</v>
       </c>
-      <c r="C138" s="16">
+      <c r="C138" s="14">
         <v>17.282191220000001</v>
       </c>
-      <c r="D138" s="11"/>
-      <c r="E138" s="17">
+      <c r="D138" s="9"/>
+      <c r="E138" s="15">
         <v>68.205100000000002</v>
       </c>
-      <c r="F138" s="17">
+      <c r="F138" s="15">
         <v>2.9487000000000001</v>
       </c>
-      <c r="G138" s="11"/>
-      <c r="H138" s="18">
+      <c r="G138" s="9"/>
+      <c r="H138" s="16">
         <v>77.972610680000003</v>
       </c>
-      <c r="I138" s="18">
+      <c r="I138" s="16">
         <v>14.95569875</v>
       </c>
-      <c r="J138" s="11"/>
-      <c r="K138" s="19">
+      <c r="J138" s="9"/>
+      <c r="K138" s="17">
         <v>79.004326860000006</v>
       </c>
-      <c r="L138" s="19">
+      <c r="L138" s="17">
         <v>10.62819777</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A139" s="11"/>
-      <c r="B139" s="16">
+      <c r="A139" s="9"/>
+      <c r="B139" s="14">
         <v>45.028997529999998</v>
       </c>
-      <c r="C139" s="16">
+      <c r="C139" s="14">
         <v>17.724447300000001</v>
       </c>
-      <c r="D139" s="11"/>
-      <c r="E139" s="17">
+      <c r="D139" s="9"/>
+      <c r="E139" s="15">
         <v>37.692300000000003</v>
       </c>
-      <c r="F139" s="17">
+      <c r="F139" s="15">
         <v>25.769200000000001</v>
       </c>
-      <c r="G139" s="11"/>
-      <c r="H139" s="18">
+      <c r="G139" s="9"/>
+      <c r="H139" s="16">
         <v>41.528919760000001</v>
       </c>
-      <c r="I139" s="18">
+      <c r="I139" s="16">
         <v>24.916425189999998</v>
       </c>
-      <c r="J139" s="11"/>
-      <c r="K139" s="19">
+      <c r="J139" s="9"/>
+      <c r="K139" s="17">
         <v>40.048186469999997</v>
       </c>
-      <c r="L139" s="19">
+      <c r="L139" s="17">
         <v>24.261487930000001</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A140" s="11"/>
-      <c r="B140" s="16">
+      <c r="A140" s="9"/>
+      <c r="B140" s="14">
         <v>39.921362809999998</v>
       </c>
-      <c r="C140" s="16">
+      <c r="C140" s="14">
         <v>19.70184953</v>
       </c>
-      <c r="D140" s="11"/>
-      <c r="E140" s="17">
+      <c r="D140" s="9"/>
+      <c r="E140" s="15">
         <v>39.487200000000001</v>
       </c>
-      <c r="F140" s="17">
+      <c r="F140" s="15">
         <v>25.384599999999999</v>
       </c>
-      <c r="G140" s="11"/>
-      <c r="H140" s="18">
+      <c r="G140" s="9"/>
+      <c r="H140" s="16">
         <v>43.7225508</v>
       </c>
-      <c r="I140" s="18">
+      <c r="I140" s="16">
         <v>19.077327799999999</v>
       </c>
-      <c r="J140" s="11"/>
-      <c r="K140" s="19">
+      <c r="J140" s="9"/>
+      <c r="K140" s="17">
         <v>34.794593540000001</v>
       </c>
-      <c r="L140" s="19">
+      <c r="L140" s="17">
         <v>13.969683460000001</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A141" s="11"/>
-      <c r="B141" s="16">
+      <c r="A141" s="9"/>
+      <c r="B141" s="14">
         <v>84.794277879999996</v>
       </c>
-      <c r="C141" s="16">
+      <c r="C141" s="14">
         <v>55.56865037</v>
       </c>
-      <c r="D141" s="11"/>
-      <c r="E141" s="17">
+      <c r="D141" s="9"/>
+      <c r="E141" s="15">
         <v>91.2821</v>
       </c>
-      <c r="F141" s="17">
+      <c r="F141" s="15">
         <v>41.538499999999999</v>
       </c>
-      <c r="G141" s="11"/>
-      <c r="H141" s="18">
+      <c r="G141" s="9"/>
+      <c r="H141" s="16">
         <v>79.326078179999996</v>
       </c>
-      <c r="I141" s="18">
+      <c r="I141" s="16">
         <v>52.900391290000002</v>
       </c>
-      <c r="J141" s="11"/>
-      <c r="K141" s="19">
+      <c r="J141" s="9"/>
+      <c r="K141" s="17">
         <v>79.221764440000001</v>
       </c>
-      <c r="L141" s="19">
+      <c r="L141" s="17">
         <v>22.094591479999998</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A142" s="11"/>
-      <c r="B142" s="16">
+      <c r="A142" s="9"/>
+      <c r="B142" s="14">
         <v>55.662958740000001</v>
       </c>
-      <c r="C142" s="16">
+      <c r="C142" s="14">
         <v>83.356479620000002</v>
       </c>
-      <c r="D142" s="11"/>
-      <c r="E142" s="17">
+      <c r="D142" s="9"/>
+      <c r="E142" s="15">
         <v>50</v>
       </c>
-      <c r="F142" s="17">
+      <c r="F142" s="15">
         <v>95.769199999999998</v>
       </c>
-      <c r="G142" s="11"/>
-      <c r="H142" s="18">
+      <c r="G142" s="9"/>
+      <c r="H142" s="16">
         <v>56.663974080000003</v>
       </c>
-      <c r="I142" s="18">
+      <c r="I142" s="16">
         <v>87.940125010000003</v>
       </c>
-      <c r="J142" s="11"/>
-      <c r="K142" s="19">
+      <c r="J142" s="9"/>
+      <c r="K142" s="17">
         <v>36.030879769999999</v>
       </c>
-      <c r="L142" s="19">
+      <c r="L142" s="17">
         <v>93.121733239999998</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A143" s="11"/>
-      <c r="B143" s="16">
+      <c r="A143" s="9"/>
+      <c r="B143" s="14">
         <v>50.492247509999999</v>
       </c>
-      <c r="C143" s="16">
+      <c r="C143" s="14">
         <v>78.997532070000005</v>
       </c>
-      <c r="D143" s="11"/>
-      <c r="E143" s="17">
+      <c r="D143" s="9"/>
+      <c r="E143" s="15">
         <v>47.948700000000002</v>
       </c>
-      <c r="F143" s="17">
+      <c r="F143" s="15">
         <v>95</v>
       </c>
-      <c r="G143" s="11"/>
-      <c r="H143" s="18">
+      <c r="G143" s="9"/>
+      <c r="H143" s="16">
         <v>57.82178923</v>
       </c>
-      <c r="I143" s="18">
+      <c r="I143" s="16">
         <v>90.693166550000001</v>
       </c>
-      <c r="J143" s="11"/>
-      <c r="K143" s="19">
+      <c r="J143" s="9"/>
+      <c r="K143" s="17">
         <v>34.499558309999998</v>
       </c>
-      <c r="L143" s="19">
+      <c r="L143" s="17">
         <v>86.609985050000006</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A144" s="11"/>
-      <c r="B144" s="16">
+      <c r="A144" s="9"/>
+      <c r="B144" s="14">
         <v>51.467101139999997</v>
       </c>
-      <c r="C144" s="16">
+      <c r="C144" s="14">
         <v>79.201844579999999</v>
       </c>
-      <c r="D144" s="11"/>
-      <c r="E144" s="17">
+      <c r="D144" s="9"/>
+      <c r="E144" s="15">
         <v>44.102600000000002</v>
       </c>
-      <c r="F144" s="17">
+      <c r="F144" s="15">
         <v>92.692300000000003</v>
       </c>
-      <c r="G144" s="11"/>
-      <c r="H144" s="18">
+      <c r="G144" s="9"/>
+      <c r="H144" s="16">
         <v>58.2431719</v>
       </c>
-      <c r="I144" s="18">
+      <c r="I144" s="16">
         <v>92.104327870000006</v>
       </c>
-      <c r="J144" s="11"/>
-      <c r="K144" s="19">
+      <c r="J144" s="9"/>
+      <c r="K144" s="17">
         <v>31.10686656</v>
       </c>
-      <c r="L144" s="19">
+      <c r="L144" s="17">
         <v>89.461635240000007</v>
       </c>
     </row>

--- a/day6.xlsx
+++ b/day6.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2A3814-C192-8A49-9BF1-7CEFBAB39984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C1A03C-A492-8347-84AA-DE5D2663CD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{AA873D0A-0169-AA4D-8FF3-837BDFA22737}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{AA873D0A-0169-AA4D-8FF3-837BDFA22737}"/>
   </bookViews>
   <sheets>
     <sheet name="agenda" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$C$68:$C$87</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet2!$C$68:$C$87</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>ADVANCE STATS</t>
   </si>
@@ -109,6 +136,36 @@
   </si>
   <si>
     <t>50% middle/Medianß</t>
+  </si>
+  <si>
+    <t>PERCENTILEs</t>
+  </si>
+  <si>
+    <t>Relative Standing ( Position/rank) expressed as percentage</t>
+  </si>
+  <si>
+    <t>QUARTILE</t>
+  </si>
+  <si>
+    <t>QUARTER</t>
+  </si>
+  <si>
+    <t>For outlier</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IQR </t>
+  </si>
+  <si>
+    <t>UPPER LIMIT</t>
+  </si>
+  <si>
+    <t>LOWER LIMIT</t>
   </si>
 </sst>
 </file>
@@ -131,7 +188,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,6 +198,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -157,20 +238,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -181,6 +278,596 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000000-A433-D04E-B079-8CEF791B2C0D}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -259,8 +946,8 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>191124</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -279,7 +966,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -324,8 +1011,8 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>54684</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -344,7 +1031,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -389,8 +1076,8 @@
       <xdr:row>47</xdr:row>
       <xdr:rowOff>79955</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Ink 26">
@@ -409,7 +1096,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Ink 26">
@@ -441,6 +1128,50 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>330602</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>159607</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{096C4926-EDDC-C6BE-09D6-783A00C8F0F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="826823" y="11095964"/>
+          <a:ext cx="1984248" cy="1975310"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -459,8 +1190,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>51555</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -479,7 +1210,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -570,6 +1301,145 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>349597</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>70554</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5427</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>58049</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="box_plot_">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6310DAB-B393-01D7-BD9A-52112D030394}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2824469" y="14529016"/>
+          <a:ext cx="3780616" cy="1393178"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>422275</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>41275</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3198D9C-F602-7AF9-029A-07D972E89BFD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5375275" y="16684625"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1100"/>
+                <a:t>This chart isn’t available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1018,18 +1888,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7ED809C-A335-DA45-8956-D9585644425C}">
-  <dimension ref="A2:E39"/>
+  <dimension ref="A2:E74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
@@ -1057,11 +1927,11 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
@@ -1105,6 +1975,40 @@
       </c>
       <c r="D39" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B72" t="str">
+        <f>" &gt; Q3 + 1.5 (Q3 - Q1)"</f>
+        <v xml:space="preserve"> &gt; Q3 + 1.5 (Q3 - Q1)</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B74" t="str">
+        <f>"&lt; Q1 - 1.5 ( Q3 - Q1 )"</f>
+        <v>&lt; Q1 - 1.5 ( Q3 - Q1 )</v>
       </c>
     </row>
   </sheetData>
@@ -1118,11 +2022,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E549A6-0D72-C748-8AC4-C3958BB72F61}">
-  <dimension ref="A2:T58"/>
+  <dimension ref="A2:T87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2">
@@ -1180,23 +2084,23 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
@@ -1291,53 +2195,53 @@
         <v>4349.3294502332965</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" ref="G21:G22" ca="1" si="2">_xlfn.FORMULATEXT(F22)</f>
+        <f t="shared" ref="G22" ca="1" si="2">_xlfn.FORMULATEXT(F22)</f>
         <v>=STDEV.S(B14:B17)</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
     </row>
     <row r="39" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C39">
         <v>29</v>
       </c>
       <c r="E39">
-        <f>PERCENTILE(C39:C58,50%)</f>
-        <v>85</v>
+        <f>PERCENTILE(C39:C58,93%)</f>
+        <v>363</v>
       </c>
       <c r="F39" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E39)</f>
-        <v>=PERCENTILE(C39:C58,50%)</v>
+        <v>=PERCENTILE(C39:C58,93%)</v>
       </c>
     </row>
     <row r="40" spans="3:6" x14ac:dyDescent="0.2">
@@ -1394,54 +2298,264 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C49">
         <v>-35</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C50">
         <v>172</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C51">
         <v>363</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C52">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C53">
         <v>350</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C54">
         <v>-32</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C55">
         <v>245</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C56">
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C57">
         <v>326</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C58">
         <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="4" t="str">
+        <f>"1/4"</f>
+        <v>1/4</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>29</v>
+      </c>
+      <c r="C68" s="5" cm="1">
+        <f t="array" ref="C68:C87">_xlfn._xlws.SORT(B68:B87)</f>
+        <v>-45</v>
+      </c>
+      <c r="D68">
+        <f>QUARTILE(B68:B87,2)</f>
+        <v>85</v>
+      </c>
+      <c r="E68" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D68)</f>
+        <v>=QUARTILE(B68:B87,2)</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B69">
+        <v>-45</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B70">
+        <v>900</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-32</v>
+      </c>
+      <c r="D70">
+        <f>PERCENTILE(B68:B87,50%)</f>
+        <v>85</v>
+      </c>
+      <c r="E70" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D70)</f>
+        <v>=PERCENTILE(B68:B87,50%)</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>363</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <v>303</v>
+      </c>
+      <c r="C72" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>-12</v>
+      </c>
+      <c r="C73" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>103</v>
+      </c>
+      <c r="C74" s="6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>51</v>
+      </c>
+      <c r="C75" s="6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>64</v>
+      </c>
+      <c r="C76" s="6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>42</v>
+      </c>
+      <c r="C77" s="6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>-35</v>
+      </c>
+      <c r="C78" s="7">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B79">
+        <v>172</v>
+      </c>
+      <c r="C79" s="7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B80">
+        <v>363</v>
+      </c>
+      <c r="C80" s="7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B81">
+        <v>32</v>
+      </c>
+      <c r="C81" s="7">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B82">
+        <v>350</v>
+      </c>
+      <c r="C82" s="7">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>-32</v>
+      </c>
+      <c r="C83" s="8">
+        <v>326</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B84">
+        <v>245</v>
+      </c>
+      <c r="C84" s="8">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>146</v>
+      </c>
+      <c r="C85" s="8">
+        <v>363</v>
+      </c>
+      <c r="E85" t="str">
+        <f>" &gt; Q3 + 1.5 (Q3 - Q1)"</f>
+        <v xml:space="preserve"> &gt; Q3 + 1.5 (Q3 - Q1)</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B86">
+        <v>326</v>
+      </c>
+      <c r="C86" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B87">
+        <v>67</v>
+      </c>
+      <c r="C87" s="8">
+        <v>900</v>
+      </c>
+      <c r="E87" t="str">
+        <f>"&lt; Q1 - 1.5 ( Q3 - Q1 )"</f>
+        <v>&lt; Q1 - 1.5 ( Q3 - Q1 )</v>
       </c>
     </row>
   </sheetData>
@@ -1451,4 +2565,155 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77659A75-C29F-A845-8AC5-C55F4BC8F2BD}">
+  <dimension ref="B5:D24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D6">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D7">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <f>QUARTILE(D5:D24,1)</f>
+        <v>31.25</v>
+      </c>
+      <c r="D8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <f>QUARTILE(D5:D24,3)</f>
+        <v>308.75</v>
+      </c>
+      <c r="D9">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <f>C9-C8</f>
+        <v>277.5</v>
+      </c>
+      <c r="D12">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D14">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15">
+        <f>C9+1.5*C12</f>
+        <v>725</v>
+      </c>
+      <c r="D15">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <f>C8-1.5*C12</f>
+        <v>-385</v>
+      </c>
+      <c r="D17">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D6:D24">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
+      <formula>$C$17</formula>
+      <formula>$C$15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>